--- a/InputData/Clean/EnvironmentalData/All-Environmental-Variables-Wide.xlsx
+++ b/InputData/Clean/EnvironmentalData/All-Environmental-Variables-Wide.xlsx
@@ -1705,6 +1705,9 @@
       <c r="I38">
         <v>-0.18</v>
       </c>
+      <c r="J38">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
@@ -1738,6 +1741,9 @@
       <c r="I39">
         <v>-0.175</v>
       </c>
+      <c r="J39">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
@@ -1771,6 +1777,9 @@
       <c r="I40">
         <v>-0.18</v>
       </c>
+      <c r="J40">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
@@ -1804,6 +1813,9 @@
       <c r="I41">
         <v>-0.19</v>
       </c>
+      <c r="J41">
+        <v>0.10036601</v>
+      </c>
       <c r="K41">
         <v>0</v>
       </c>
@@ -1840,6 +1852,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J42">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
@@ -1855,6 +1870,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J43">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
@@ -1888,6 +1906,9 @@
       <c r="I44">
         <v>-0.19</v>
       </c>
+      <c r="J44">
+        <v>0.10036601</v>
+      </c>
       <c r="K44">
         <v>0</v>
       </c>
@@ -1942,6 +1963,9 @@
       <c r="I45">
         <v>-0.14</v>
       </c>
+      <c r="J45">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
@@ -1975,6 +1999,9 @@
       <c r="I46">
         <v>-0.2</v>
       </c>
+      <c r="J46">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
@@ -2008,6 +2035,9 @@
       <c r="I47">
         <v>-0.2</v>
       </c>
+      <c r="J47">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
@@ -2041,6 +2071,9 @@
       <c r="I48">
         <v>-0.2</v>
       </c>
+      <c r="J48">
+        <v>0.10036601</v>
+      </c>
       <c r="K48">
         <v>0</v>
       </c>
@@ -2077,6 +2110,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J49">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
@@ -2092,6 +2128,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J50">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
@@ -2125,6 +2164,9 @@
       <c r="I51">
         <v>-0.19</v>
       </c>
+      <c r="J51">
+        <v>0.10036601</v>
+      </c>
       <c r="K51">
         <v>0</v>
       </c>
@@ -2179,6 +2221,9 @@
       <c r="I52">
         <v>-0.18</v>
       </c>
+      <c r="J52">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
@@ -2195,7 +2240,7 @@
         </is>
       </c>
       <c r="J53">
-        <v>0.1003660100008334</v>
+        <v>0.10036601</v>
       </c>
     </row>
     <row r="54">
@@ -2212,6 +2257,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J54">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
@@ -2227,6 +2275,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J55">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
@@ -2242,6 +2293,9 @@
           <t>PBR</t>
         </is>
       </c>
+      <c r="J56">
+        <v>0.10036601</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
@@ -2256,6 +2310,9 @@
         <is>
           <t>PBR</t>
         </is>
+      </c>
+      <c r="J57">
+        <v>0.10036601</v>
       </c>
     </row>
     <row r="58">

--- a/InputData/Clean/EnvironmentalData/All-Environmental-Variables-Wide.xlsx
+++ b/InputData/Clean/EnvironmentalData/All-Environmental-Variables-Wide.xlsx
@@ -6616,6 +6616,9 @@
       <c r="F191">
         <v>7.84</v>
       </c>
+      <c r="J191">
+        <v>3.4128</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2">
@@ -8755,6 +8758,9 @@
       <c r="I259">
         <v>-1.15</v>
       </c>
+      <c r="J259">
+        <v>2.9376</v>
+      </c>
       <c r="K259">
         <v>0</v>
       </c>
@@ -8959,6 +8965,9 @@
       <c r="I264">
         <v>-5.45</v>
       </c>
+      <c r="J264">
+        <v>2.8944</v>
+      </c>
       <c r="K264">
         <v>0</v>
       </c>
@@ -9163,6 +9172,9 @@
       <c r="I269">
         <v>-5.46</v>
       </c>
+      <c r="J269">
+        <v>0.864</v>
+      </c>
       <c r="K269">
         <v>1</v>
       </c>
@@ -10081,6 +10093,9 @@
       <c r="I292">
         <v>-0.62</v>
       </c>
+      <c r="J292">
+        <v>1.7712</v>
+      </c>
       <c r="K292">
         <v>0</v>
       </c>
@@ -10255,6 +10270,9 @@
       <c r="I296">
         <v>-0.63</v>
       </c>
+      <c r="J296">
+        <v>1.6848</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2">
@@ -10375,6 +10393,9 @@
       <c r="I299">
         <v>2.95</v>
       </c>
+      <c r="J299">
+        <v>2.7216</v>
+      </c>
       <c r="K299">
         <v>0</v>
       </c>
@@ -11332,6 +11353,9 @@
       <c r="I323">
         <v>-1.26</v>
       </c>
+      <c r="J323">
+        <v>3.024</v>
+      </c>
       <c r="K323">
         <v>9</v>
       </c>
@@ -11746,6 +11770,9 @@
       <c r="I333">
         <v>-3.255</v>
       </c>
+      <c r="J333">
+        <v>2.6784</v>
+      </c>
       <c r="K333">
         <v>0</v>
       </c>
@@ -11953,6 +11980,9 @@
       <c r="I338">
         <v>-3.26</v>
       </c>
+      <c r="J338">
+        <v>2.8512</v>
+      </c>
       <c r="K338">
         <v>0</v>
       </c>
@@ -12073,6 +12103,9 @@
       <c r="I341">
         <v>-3.17</v>
       </c>
+      <c r="J341">
+        <v>2.7216</v>
+      </c>
       <c r="K341">
         <v>0</v>
       </c>
@@ -12378,6 +12411,9 @@
       </c>
       <c r="I349">
         <v>-3.32</v>
+      </c>
+      <c r="J349">
+        <v>3.2832</v>
       </c>
       <c r="K349">
         <v>0</v>

--- a/InputData/Clean/EnvironmentalData/All-Environmental-Variables-Wide.xlsx
+++ b/InputData/Clean/EnvironmentalData/All-Environmental-Variables-Wide.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S349"/>
+  <dimension ref="A1:S307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -6310,11 +6310,11 @@
     </row>
     <row r="182">
       <c r="A182" s="2">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6323,22 +6323,22 @@
         </is>
       </c>
       <c r="D182">
-        <v>24.16666666666667</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E182">
-        <v>33.44</v>
+        <v>33.59</v>
       </c>
       <c r="F182">
-        <v>8.039999999999999</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6347,22 +6347,40 @@
         </is>
       </c>
       <c r="D183">
-        <v>24.11111111111111</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E183">
-        <v>33.59</v>
+        <v>33.42</v>
       </c>
       <c r="F183">
-        <v>8.07</v>
+        <v>7.92</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0.16</v>
+      </c>
+      <c r="M183">
+        <v>1.5</v>
+      </c>
+      <c r="N183">
+        <v>2</v>
+      </c>
+      <c r="P183">
+        <v>0.3</v>
+      </c>
+      <c r="Q183">
+        <v>0.005</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6374,37 +6392,37 @@
         <v>24.05555555555556</v>
       </c>
       <c r="E184">
-        <v>33.42</v>
+        <v>33.94</v>
       </c>
       <c r="F184">
-        <v>7.92</v>
+        <v>7.86</v>
       </c>
       <c r="K184">
         <v>0</v>
       </c>
       <c r="L184">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="M184">
         <v>1.5</v>
       </c>
       <c r="N184">
-        <v>2</v>
-      </c>
-      <c r="P184">
-        <v>0.3</v>
-      </c>
-      <c r="Q184">
-        <v>0.005</v>
+        <v>2.1</v>
+      </c>
+      <c r="R184">
+        <v>0</v>
+      </c>
+      <c r="S184">
+        <v>355</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6413,40 +6431,22 @@
         </is>
       </c>
       <c r="D185">
-        <v>24.05555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E185">
         <v>33.94</v>
       </c>
       <c r="F185">
-        <v>7.86</v>
-      </c>
-      <c r="K185">
-        <v>0</v>
-      </c>
-      <c r="L185">
-        <v>0.04</v>
-      </c>
-      <c r="M185">
-        <v>1.5</v>
-      </c>
-      <c r="N185">
-        <v>2.1</v>
-      </c>
-      <c r="R185">
-        <v>0</v>
-      </c>
-      <c r="S185">
-        <v>355</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6455,22 +6455,22 @@
         </is>
       </c>
       <c r="D186">
-        <v>24.16666666666667</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E186">
-        <v>33.94</v>
+        <v>33.43</v>
       </c>
       <c r="F186">
-        <v>7.93</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2">
-        <v>45448</v>
+        <v>45449</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6482,19 +6482,19 @@
         <v>24.05555555555556</v>
       </c>
       <c r="E187">
-        <v>33.43</v>
+        <v>33.37</v>
       </c>
       <c r="F187">
-        <v>7.88</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6503,22 +6503,40 @@
         </is>
       </c>
       <c r="D188">
-        <v>24.05555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E188">
-        <v>33.37</v>
+        <v>33.72</v>
       </c>
       <c r="F188">
-        <v>7.95</v>
+        <v>7.92</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0.03</v>
+      </c>
+      <c r="M188">
+        <v>1.9</v>
+      </c>
+      <c r="N188">
+        <v>3.1</v>
+      </c>
+      <c r="P188">
+        <v>0.14</v>
+      </c>
+      <c r="Q188">
+        <v>0.004</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2">
-        <v>45450</v>
+        <v>45453</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6530,37 +6548,34 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E189">
-        <v>33.72</v>
+        <v>34.94</v>
       </c>
       <c r="F189">
-        <v>7.92</v>
+        <v>7.86</v>
       </c>
       <c r="K189">
         <v>0</v>
       </c>
       <c r="L189">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="M189">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N189">
-        <v>3.1</v>
-      </c>
-      <c r="P189">
-        <v>0.14</v>
-      </c>
-      <c r="Q189">
-        <v>0.004</v>
+        <v>3.4</v>
+      </c>
+      <c r="R189">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2">
-        <v>45453</v>
+        <v>45455</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6569,37 +6584,25 @@
         </is>
       </c>
       <c r="D190">
-        <v>24.11111111111111</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E190">
-        <v>34.94</v>
+        <v>34.4</v>
       </c>
       <c r="F190">
-        <v>7.86</v>
-      </c>
-      <c r="K190">
-        <v>0</v>
-      </c>
-      <c r="L190">
-        <v>0.04</v>
-      </c>
-      <c r="M190">
-        <v>2.5</v>
-      </c>
-      <c r="N190">
-        <v>3.4</v>
-      </c>
-      <c r="R190">
-        <v>0</v>
+        <v>7.84</v>
+      </c>
+      <c r="J190">
+        <v>3.4128</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6608,25 +6611,22 @@
         </is>
       </c>
       <c r="D191">
-        <v>24.05555555555556</v>
+        <v>24.27777777777778</v>
       </c>
       <c r="E191">
-        <v>34.4</v>
+        <v>34.53</v>
       </c>
       <c r="F191">
-        <v>7.84</v>
-      </c>
-      <c r="J191">
-        <v>3.4128</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 1 Control</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6635,22 +6635,40 @@
         </is>
       </c>
       <c r="D192">
-        <v>24.27777777777778</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E192">
-        <v>34.53</v>
+        <v>33.66</v>
       </c>
       <c r="F192">
-        <v>7.87</v>
+        <v>7.89</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0.12</v>
+      </c>
+      <c r="M192">
+        <v>1.6</v>
+      </c>
+      <c r="N192">
+        <v>2.8</v>
+      </c>
+      <c r="P192">
+        <v>0.29</v>
+      </c>
+      <c r="Q192">
+        <v>0.013</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2">
-        <v>45457</v>
+        <v>45463</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6659,40 +6677,22 @@
         </is>
       </c>
       <c r="D193">
-        <v>24.22222222222222</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E193">
-        <v>33.66</v>
+        <v>32.83</v>
       </c>
       <c r="F193">
-        <v>7.89</v>
-      </c>
-      <c r="K193">
-        <v>0</v>
-      </c>
-      <c r="L193">
-        <v>0.12</v>
-      </c>
-      <c r="M193">
-        <v>1.6</v>
-      </c>
-      <c r="N193">
-        <v>2.8</v>
-      </c>
-      <c r="P193">
-        <v>0.29</v>
-      </c>
-      <c r="Q193">
-        <v>0.013</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2">
-        <v>45463</v>
+        <v>45467</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6701,22 +6701,40 @@
         </is>
       </c>
       <c r="D194">
-        <v>24.05555555555556</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E194">
-        <v>32.83</v>
+        <v>33.58</v>
       </c>
       <c r="F194">
-        <v>7.88</v>
+        <v>7.83</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0.03</v>
+      </c>
+      <c r="M194">
+        <v>1.6</v>
+      </c>
+      <c r="N194">
+        <v>2.7</v>
+      </c>
+      <c r="O194">
+        <v>106</v>
+      </c>
+      <c r="R194">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2">
-        <v>45467</v>
+        <v>45468</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6725,40 +6743,22 @@
         </is>
       </c>
       <c r="D195">
-        <v>24.22222222222222</v>
+        <v>-6.944444444444445</v>
       </c>
       <c r="E195">
-        <v>33.58</v>
+        <v>33.17</v>
       </c>
       <c r="F195">
-        <v>7.83</v>
-      </c>
-      <c r="K195">
-        <v>0</v>
-      </c>
-      <c r="L195">
-        <v>0.03</v>
-      </c>
-      <c r="M195">
-        <v>1.6</v>
-      </c>
-      <c r="N195">
-        <v>2.7</v>
-      </c>
-      <c r="O195">
-        <v>106</v>
-      </c>
-      <c r="R195">
-        <v>0</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2">
-        <v>45468</v>
+        <v>45469</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6767,22 +6767,22 @@
         </is>
       </c>
       <c r="D196">
-        <v>-6.944444444444445</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="E196">
-        <v>33.17</v>
+        <v>33.22</v>
       </c>
       <c r="F196">
-        <v>7.86</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2">
-        <v>45469</v>
+        <v>45470</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6791,22 +6791,22 @@
         </is>
       </c>
       <c r="D197">
-        <v>24.33333333333333</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E197">
-        <v>33.22</v>
+        <v>33.19</v>
       </c>
       <c r="F197">
-        <v>7.8</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2">
-        <v>45470</v>
+        <v>45471</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6815,22 +6815,43 @@
         </is>
       </c>
       <c r="D198">
-        <v>24.11111111111111</v>
+        <v>24.27777777777778</v>
       </c>
       <c r="E198">
-        <v>33.19</v>
+        <v>33.52</v>
       </c>
       <c r="F198">
-        <v>7.87</v>
+        <v>7.85</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0.18</v>
+      </c>
+      <c r="M198">
+        <v>1.3</v>
+      </c>
+      <c r="N198">
+        <v>1.7</v>
+      </c>
+      <c r="O198">
+        <v>112</v>
+      </c>
+      <c r="P198">
+        <v>0.21</v>
+      </c>
+      <c r="Q198">
+        <v>0.004</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2">
-        <v>45471</v>
+        <v>45474</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6839,19 +6860,19 @@
         </is>
       </c>
       <c r="D199">
-        <v>24.27777777777778</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E199">
-        <v>33.52</v>
+        <v>33.48</v>
       </c>
       <c r="F199">
-        <v>7.85</v>
+        <v>7.82</v>
       </c>
       <c r="K199">
         <v>0</v>
       </c>
       <c r="L199">
-        <v>0.18</v>
+        <v>0.03</v>
       </c>
       <c r="M199">
         <v>1.3</v>
@@ -6860,22 +6881,19 @@
         <v>1.7</v>
       </c>
       <c r="O199">
-        <v>112</v>
-      </c>
-      <c r="P199">
-        <v>0.21</v>
-      </c>
-      <c r="Q199">
-        <v>0.004</v>
+        <v>120</v>
+      </c>
+      <c r="R199">
+        <v>0.02</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6887,37 +6905,19 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E200">
-        <v>33.48</v>
+        <v>33.4</v>
       </c>
       <c r="F200">
-        <v>7.82</v>
-      </c>
-      <c r="K200">
-        <v>0</v>
-      </c>
-      <c r="L200">
-        <v>0.03</v>
-      </c>
-      <c r="M200">
-        <v>1.3</v>
-      </c>
-      <c r="N200">
-        <v>1.7</v>
-      </c>
-      <c r="O200">
-        <v>120</v>
-      </c>
-      <c r="R200">
-        <v>0.02</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2">
-        <v>45475</v>
+        <v>45476</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6926,22 +6926,22 @@
         </is>
       </c>
       <c r="D201">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E201">
-        <v>33.4</v>
+        <v>33.43</v>
       </c>
       <c r="F201">
-        <v>7.84</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2">
-        <v>45476</v>
+        <v>45478</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6950,22 +6950,37 @@
         </is>
       </c>
       <c r="D202">
-        <v>24.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="E202">
-        <v>33.43</v>
+        <v>33.37</v>
       </c>
       <c r="F202">
         <v>7.85</v>
       </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0.01</v>
+      </c>
+      <c r="M202">
+        <v>1.6</v>
+      </c>
+      <c r="N202">
+        <v>3.2</v>
+      </c>
+      <c r="O202">
+        <v>119</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6974,37 +6989,40 @@
         </is>
       </c>
       <c r="D203">
-        <v>24</v>
+        <v>23.44444444444444</v>
       </c>
       <c r="E203">
-        <v>33.37</v>
+        <v>33.57</v>
       </c>
       <c r="F203">
-        <v>7.85</v>
+        <v>7.83</v>
       </c>
       <c r="K203">
         <v>0</v>
       </c>
       <c r="L203">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M203">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="N203">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="O203">
-        <v>119</v>
+        <v>136</v>
+      </c>
+      <c r="R203">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 1  Control</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7013,40 +7031,22 @@
         </is>
       </c>
       <c r="D204">
-        <v>23.44444444444444</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E204">
-        <v>33.57</v>
+        <v>33.3</v>
       </c>
       <c r="F204">
-        <v>7.83</v>
-      </c>
-      <c r="K204">
-        <v>0</v>
-      </c>
-      <c r="L204">
-        <v>0.03</v>
-      </c>
-      <c r="M204">
-        <v>1.4</v>
-      </c>
-      <c r="N204">
-        <v>2</v>
-      </c>
-      <c r="O204">
-        <v>136</v>
-      </c>
-      <c r="R204">
-        <v>0</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2">
-        <v>45482</v>
+        <v>45483</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7055,22 +7055,22 @@
         </is>
       </c>
       <c r="D205">
-        <v>24.22222222222222</v>
+        <v>24</v>
       </c>
       <c r="E205">
-        <v>33.3</v>
+        <v>33.36</v>
       </c>
       <c r="F205">
-        <v>7.73</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7079,22 +7079,22 @@
         </is>
       </c>
       <c r="D206">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E206">
-        <v>33.36</v>
+        <v>33.4</v>
       </c>
       <c r="F206">
-        <v>7.74</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2">
-        <v>45484</v>
+        <v>45485</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7106,19 +7106,40 @@
         <v>24.16666666666667</v>
       </c>
       <c r="E207">
-        <v>33.4</v>
+        <v>33.27</v>
       </c>
       <c r="F207">
-        <v>7.71</v>
+        <v>7.72</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0.01</v>
+      </c>
+      <c r="M207">
+        <v>1.6</v>
+      </c>
+      <c r="N207">
+        <v>2.3</v>
+      </c>
+      <c r="O207">
+        <v>120</v>
+      </c>
+      <c r="P207">
+        <v>0.31</v>
+      </c>
+      <c r="Q207">
+        <v>0.007</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2">
-        <v>45485</v>
+        <v>45488</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7130,40 +7151,40 @@
         <v>24.16666666666667</v>
       </c>
       <c r="E208">
-        <v>33.27</v>
+        <v>34.81</v>
       </c>
       <c r="F208">
-        <v>7.72</v>
+        <v>7.86</v>
       </c>
       <c r="K208">
         <v>0</v>
       </c>
       <c r="L208">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M208">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="N208">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="O208">
-        <v>120</v>
-      </c>
-      <c r="P208">
-        <v>0.31</v>
-      </c>
-      <c r="Q208">
-        <v>0.007</v>
+        <v>102</v>
+      </c>
+      <c r="R208">
+        <v>0.06</v>
+      </c>
+      <c r="S208">
+        <v>370</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2">
-        <v>45488</v>
+        <v>45489</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7172,43 +7193,22 @@
         </is>
       </c>
       <c r="D209">
-        <v>24.16666666666667</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E209">
-        <v>34.81</v>
+        <v>33.98</v>
       </c>
       <c r="F209">
-        <v>7.86</v>
-      </c>
-      <c r="K209">
-        <v>0</v>
-      </c>
-      <c r="L209">
-        <v>0</v>
-      </c>
-      <c r="M209">
-        <v>1.2</v>
-      </c>
-      <c r="N209">
-        <v>1</v>
-      </c>
-      <c r="O209">
-        <v>102</v>
-      </c>
-      <c r="R209">
-        <v>0.06</v>
-      </c>
-      <c r="S209">
-        <v>370</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2">
-        <v>45489</v>
+        <v>45490</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="D210">
-        <v>24.22222222222222</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E210">
-        <v>33.98</v>
+        <v>33.95</v>
       </c>
       <c r="F210">
         <v>7.88</v>
@@ -7228,11 +7228,11 @@
     </row>
     <row r="211">
       <c r="A211" s="2">
-        <v>45490</v>
+        <v>45491</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7244,19 +7244,19 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E211">
-        <v>33.95</v>
+        <v>34.06</v>
       </c>
       <c r="F211">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7265,22 +7265,43 @@
         </is>
       </c>
       <c r="D212">
-        <v>24.11111111111111</v>
+        <v>24.27777777777778</v>
       </c>
       <c r="E212">
-        <v>34.06</v>
+        <v>33.45</v>
       </c>
       <c r="F212">
-        <v>7.86</v>
+        <v>7.87</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0.03</v>
+      </c>
+      <c r="M212">
+        <v>1.6</v>
+      </c>
+      <c r="N212">
+        <v>2.3</v>
+      </c>
+      <c r="O212">
+        <v>103</v>
+      </c>
+      <c r="P212">
+        <v>0.22</v>
+      </c>
+      <c r="Q212">
+        <v>0.008</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2">
-        <v>45492</v>
+        <v>45495</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7289,43 +7310,43 @@
         </is>
       </c>
       <c r="D213">
-        <v>24.27777777777778</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E213">
-        <v>33.45</v>
+        <v>33.11</v>
       </c>
       <c r="F213">
-        <v>7.87</v>
+        <v>7.84</v>
       </c>
       <c r="K213">
         <v>0</v>
       </c>
       <c r="L213">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M213">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="N213">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="O213">
-        <v>103</v>
-      </c>
-      <c r="P213">
-        <v>0.22</v>
-      </c>
-      <c r="Q213">
-        <v>0.008</v>
+        <v>111</v>
+      </c>
+      <c r="R213">
+        <v>0.04</v>
+      </c>
+      <c r="S213">
+        <v>362</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7337,40 +7358,19 @@
         <v>24.16666666666667</v>
       </c>
       <c r="E214">
-        <v>33.11</v>
+        <v>32.84</v>
       </c>
       <c r="F214">
-        <v>7.84</v>
-      </c>
-      <c r="K214">
-        <v>0</v>
-      </c>
-      <c r="L214">
-        <v>0.02</v>
-      </c>
-      <c r="M214">
-        <v>1.4</v>
-      </c>
-      <c r="N214">
-        <v>1.9</v>
-      </c>
-      <c r="O214">
-        <v>111</v>
-      </c>
-      <c r="R214">
-        <v>0.04</v>
-      </c>
-      <c r="S214">
-        <v>362</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2">
-        <v>45496</v>
+        <v>45497</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7382,19 +7382,19 @@
         <v>24.16666666666667</v>
       </c>
       <c r="E215">
-        <v>32.84</v>
+        <v>33.02</v>
       </c>
       <c r="F215">
-        <v>7.88</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2">
-        <v>45497</v>
+        <v>45499</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7406,19 +7406,40 @@
         <v>24.16666666666667</v>
       </c>
       <c r="E216">
-        <v>33.02</v>
+        <v>33.13</v>
       </c>
       <c r="F216">
         <v>7.87</v>
       </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0.02</v>
+      </c>
+      <c r="M216">
+        <v>2</v>
+      </c>
+      <c r="N216">
+        <v>2.7</v>
+      </c>
+      <c r="O216">
+        <v>121</v>
+      </c>
+      <c r="P216">
+        <v>0.62</v>
+      </c>
+      <c r="Q216">
+        <v>0.019</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2">
-        <v>45499</v>
+        <v>45502</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 2  Control</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7427,43 +7448,22 @@
         </is>
       </c>
       <c r="D217">
-        <v>24.16666666666667</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E217">
-        <v>33.13</v>
+        <v>33.87</v>
       </c>
       <c r="F217">
         <v>7.87</v>
       </c>
-      <c r="K217">
-        <v>0</v>
-      </c>
-      <c r="L217">
-        <v>0.02</v>
-      </c>
-      <c r="M217">
-        <v>2</v>
-      </c>
-      <c r="N217">
-        <v>2.7</v>
-      </c>
-      <c r="O217">
-        <v>121</v>
-      </c>
-      <c r="P217">
-        <v>0.62</v>
-      </c>
-      <c r="Q217">
-        <v>0.019</v>
-      </c>
     </row>
     <row r="218">
       <c r="A218" s="2">
-        <v>45502</v>
+        <v>45566</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7472,22 +7472,31 @@
         </is>
       </c>
       <c r="D218">
-        <v>24.22222222222222</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E218">
-        <v>33.87</v>
+        <v>34.08</v>
       </c>
       <c r="F218">
-        <v>7.87</v>
+        <v>7.96</v>
+      </c>
+      <c r="G218">
+        <v>199.7</v>
+      </c>
+      <c r="H218">
+        <v>-4.72</v>
+      </c>
+      <c r="I218">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2">
-        <v>45503</v>
+        <v>45567</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7496,22 +7505,31 @@
         </is>
       </c>
       <c r="D219">
-        <v>24.22222222222222</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E219">
-        <v>34</v>
+        <v>34.32</v>
       </c>
       <c r="F219">
-        <v>7.87</v>
+        <v>7.95</v>
+      </c>
+      <c r="G219">
+        <v>168.3</v>
+      </c>
+      <c r="H219">
+        <v>-4.33</v>
+      </c>
+      <c r="I219">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2">
-        <v>45504</v>
+        <v>45568</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7520,22 +7538,31 @@
         </is>
       </c>
       <c r="D220">
-        <v>24.11111111111111</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E220">
-        <v>34.12</v>
+        <v>33.93</v>
       </c>
       <c r="F220">
-        <v>7.84</v>
+        <v>8.02</v>
+      </c>
+      <c r="G220">
+        <v>153.7</v>
+      </c>
+      <c r="H220">
+        <v>-1.41</v>
+      </c>
+      <c r="I220">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2">
-        <v>45505</v>
+        <v>45569</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7544,22 +7571,52 @@
         </is>
       </c>
       <c r="D221">
-        <v>23.83333333333334</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E221">
-        <v>34.33</v>
+        <v>34.38</v>
       </c>
       <c r="F221">
-        <v>7.86</v>
+        <v>7.84</v>
+      </c>
+      <c r="G221">
+        <v>159.2</v>
+      </c>
+      <c r="H221">
+        <v>-5.9</v>
+      </c>
+      <c r="I221">
+        <v>-1.3</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+      <c r="M221">
+        <v>1.5</v>
+      </c>
+      <c r="N221">
+        <v>2.1</v>
+      </c>
+      <c r="O221">
+        <v>90</v>
+      </c>
+      <c r="P221">
+        <v>0.2</v>
+      </c>
+      <c r="Q221">
+        <v>0.014</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2">
-        <v>45506</v>
+        <v>45572</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7568,43 +7625,52 @@
         </is>
       </c>
       <c r="D222">
-        <v>24.16666666666667</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E222">
-        <v>33.43</v>
+        <v>34.91</v>
       </c>
       <c r="F222">
-        <v>7.86</v>
+        <v>7.82</v>
+      </c>
+      <c r="G222">
+        <v>165.6</v>
+      </c>
+      <c r="H222">
+        <v>-4.85</v>
+      </c>
+      <c r="I222">
+        <v>-5.45</v>
+      </c>
+      <c r="J222">
+        <v>2.8944</v>
       </c>
       <c r="K222">
         <v>0</v>
       </c>
       <c r="L222">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M222">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="N222">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O222">
-        <v>108</v>
-      </c>
-      <c r="P222">
-        <v>0.22</v>
-      </c>
-      <c r="Q222">
-        <v>0.054</v>
+        <v>82</v>
+      </c>
+      <c r="R222">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2">
-        <v>45509</v>
+        <v>45573</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7613,43 +7679,31 @@
         </is>
       </c>
       <c r="D223">
-        <v>24.22222222222222</v>
+        <v>24</v>
       </c>
       <c r="E223">
-        <v>34.36</v>
+        <v>34.57</v>
       </c>
       <c r="F223">
-        <v>7.85</v>
-      </c>
-      <c r="K223">
-        <v>0</v>
-      </c>
-      <c r="L223">
-        <v>0.02</v>
-      </c>
-      <c r="M223">
-        <v>1.6</v>
-      </c>
-      <c r="N223">
-        <v>2.5</v>
-      </c>
-      <c r="O223">
-        <v>112</v>
-      </c>
-      <c r="R223">
-        <v>0</v>
-      </c>
-      <c r="S223">
-        <v>309</v>
+        <v>7.95</v>
+      </c>
+      <c r="G223">
+        <v>149.1</v>
+      </c>
+      <c r="H223">
+        <v>-3.95</v>
+      </c>
+      <c r="I223">
+        <v>-5.46</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2">
-        <v>45510</v>
+        <v>45574</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7661,19 +7715,28 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E224">
-        <v>34.03</v>
+        <v>34.78</v>
       </c>
       <c r="F224">
-        <v>7.85</v>
+        <v>7.9</v>
+      </c>
+      <c r="G224">
+        <v>174.5</v>
+      </c>
+      <c r="H224">
+        <v>-3.97</v>
+      </c>
+      <c r="I224">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2">
-        <v>45511</v>
+        <v>45575</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7682,22 +7745,31 @@
         </is>
       </c>
       <c r="D225">
-        <v>23.88888888888889</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E225">
-        <v>33.93</v>
+        <v>34.91</v>
       </c>
       <c r="F225">
-        <v>7.8</v>
+        <v>7.93</v>
+      </c>
+      <c r="G225">
+        <v>145.4</v>
+      </c>
+      <c r="H225">
+        <v>-4.12</v>
+      </c>
+      <c r="I225">
+        <v>-5.45</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2">
-        <v>45512</v>
+        <v>45576</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7706,22 +7778,52 @@
         </is>
       </c>
       <c r="D226">
-        <v>24.22222222222222</v>
+        <v>24</v>
       </c>
       <c r="E226">
-        <v>33.96</v>
+        <v>34.85</v>
       </c>
       <c r="F226">
-        <v>7.85</v>
+        <v>7.86</v>
+      </c>
+      <c r="G226">
+        <v>158.8</v>
+      </c>
+      <c r="H226">
+        <v>-6.04</v>
+      </c>
+      <c r="I226">
+        <v>-5.45</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0.08</v>
+      </c>
+      <c r="M226">
+        <v>1.5</v>
+      </c>
+      <c r="N226">
+        <v>1.7</v>
+      </c>
+      <c r="O226">
+        <v>81</v>
+      </c>
+      <c r="P226">
+        <v>0.19</v>
+      </c>
+      <c r="Q226">
+        <v>0.013</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2">
-        <v>45513</v>
+        <v>45579</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7730,43 +7832,52 @@
         </is>
       </c>
       <c r="D227">
-        <v>23.83333333333334</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E227">
-        <v>33.69</v>
+        <v>34.79</v>
       </c>
       <c r="F227">
-        <v>7.83</v>
+        <v>7.82</v>
+      </c>
+      <c r="G227">
+        <v>158.2</v>
+      </c>
+      <c r="H227">
+        <v>-5.87</v>
+      </c>
+      <c r="I227">
+        <v>-5.46</v>
+      </c>
+      <c r="J227">
+        <v>0.864</v>
       </c>
       <c r="K227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L227">
         <v>0.02</v>
       </c>
       <c r="M227">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N227">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O227">
-        <v>104</v>
-      </c>
-      <c r="P227">
-        <v>0.3</v>
-      </c>
-      <c r="Q227">
-        <v>0.032</v>
+        <v>96</v>
+      </c>
+      <c r="R227">
+        <v>0.01</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2">
-        <v>45516</v>
+        <v>45580</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7775,43 +7886,31 @@
         </is>
       </c>
       <c r="D228">
-        <v>24.11111111111111</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E228">
-        <v>33.4</v>
+        <v>34.51</v>
       </c>
       <c r="F228">
-        <v>7.97</v>
-      </c>
-      <c r="K228">
-        <v>0</v>
-      </c>
-      <c r="L228">
-        <v>0.03</v>
-      </c>
-      <c r="M228">
-        <v>1.5</v>
-      </c>
-      <c r="N228">
-        <v>2.1</v>
-      </c>
-      <c r="O228">
-        <v>104</v>
-      </c>
-      <c r="R228">
-        <v>0</v>
-      </c>
-      <c r="S228">
-        <v>302</v>
+        <v>7.98</v>
+      </c>
+      <c r="G228">
+        <v>156.8</v>
+      </c>
+      <c r="H228">
+        <v>-6.03</v>
+      </c>
+      <c r="I228">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2">
-        <v>45517</v>
+        <v>45581</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7820,22 +7919,31 @@
         </is>
       </c>
       <c r="D229">
-        <v>24.16666666666667</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E229">
-        <v>32.86</v>
+        <v>34.76</v>
       </c>
       <c r="F229">
-        <v>7.96</v>
+        <v>7.97</v>
+      </c>
+      <c r="G229">
+        <v>143.6</v>
+      </c>
+      <c r="H229">
+        <v>-4.27</v>
+      </c>
+      <c r="I229">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2">
-        <v>45518</v>
+        <v>45582</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7847,19 +7955,28 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E230">
-        <v>32.97</v>
+        <v>34.97</v>
       </c>
       <c r="F230">
-        <v>7.88</v>
+        <v>7.92</v>
+      </c>
+      <c r="G230">
+        <v>167.4</v>
+      </c>
+      <c r="H230">
+        <v>-4.33</v>
+      </c>
+      <c r="I230">
+        <v>-5.44</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2">
-        <v>45519</v>
+        <v>45583</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7868,22 +7985,52 @@
         </is>
       </c>
       <c r="D231">
-        <v>24</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E231">
-        <v>33.14</v>
+        <v>35.08</v>
       </c>
       <c r="F231">
-        <v>7.92</v>
+        <v>7.91</v>
+      </c>
+      <c r="G231">
+        <v>150.8</v>
+      </c>
+      <c r="H231">
+        <v>-4.63</v>
+      </c>
+      <c r="I231">
+        <v>-5.45</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+      <c r="M231">
+        <v>1.3</v>
+      </c>
+      <c r="N231">
+        <v>1.7</v>
+      </c>
+      <c r="O231">
+        <v>90</v>
+      </c>
+      <c r="P231">
+        <v>1.17</v>
+      </c>
+      <c r="Q231">
+        <v>0.118</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2">
-        <v>45520</v>
+        <v>45586</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7892,13 +8039,22 @@
         </is>
       </c>
       <c r="D232">
-        <v>23.88888888888889</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E232">
-        <v>33.29</v>
+        <v>35.95</v>
       </c>
       <c r="F232">
-        <v>7.88</v>
+        <v>7.89</v>
+      </c>
+      <c r="G232">
+        <v>176.2</v>
+      </c>
+      <c r="H232">
+        <v>-5.76</v>
+      </c>
+      <c r="I232">
+        <v>-5.48</v>
       </c>
       <c r="K232">
         <v>0</v>
@@ -7907,28 +8063,25 @@
         <v>0</v>
       </c>
       <c r="M232">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="N232">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="O232">
-        <v>109</v>
-      </c>
-      <c r="P232">
-        <v>0.29</v>
-      </c>
-      <c r="Q232">
-        <v>0.132</v>
+        <v>88</v>
+      </c>
+      <c r="R232">
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2">
-        <v>45523</v>
+        <v>45587</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7937,22 +8090,31 @@
         </is>
       </c>
       <c r="D233">
-        <v>23.77777777777778</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E233">
-        <v>33.61</v>
+        <v>34.91</v>
       </c>
       <c r="F233">
-        <v>7.89</v>
+        <v>7.96</v>
+      </c>
+      <c r="G233">
+        <v>201.5</v>
+      </c>
+      <c r="H233">
+        <v>-4.85</v>
+      </c>
+      <c r="I233">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2">
-        <v>45525</v>
+        <v>45588</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7961,22 +8123,31 @@
         </is>
       </c>
       <c r="D234">
-        <v>24.05555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E234">
-        <v>33.05</v>
+        <v>35.21</v>
       </c>
       <c r="F234">
-        <v>8.029999999999999</v>
+        <v>7.98</v>
+      </c>
+      <c r="G234">
+        <v>201.3</v>
+      </c>
+      <c r="H234">
+        <v>-5.17</v>
+      </c>
+      <c r="I234">
+        <v>-5.46</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2">
-        <v>45526</v>
+        <v>45589</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7985,22 +8156,31 @@
         </is>
       </c>
       <c r="D235">
-        <v>24.05555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E235">
-        <v>33.15</v>
+        <v>35.5</v>
       </c>
       <c r="F235">
-        <v>7.89</v>
+        <v>7.99</v>
+      </c>
+      <c r="G235">
+        <v>207</v>
+      </c>
+      <c r="H235">
+        <v>-3.68</v>
+      </c>
+      <c r="I235">
+        <v>-5.44</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2">
-        <v>45527</v>
+        <v>45590</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8009,22 +8189,52 @@
         </is>
       </c>
       <c r="D236">
-        <v>24.05555555555556</v>
+        <v>24.13888888888889</v>
       </c>
       <c r="E236">
-        <v>33.34</v>
+        <v>34.19499999999999</v>
       </c>
       <c r="F236">
-        <v>7.89</v>
+        <v>7.91</v>
+      </c>
+      <c r="G236">
+        <v>245.75</v>
+      </c>
+      <c r="H236">
+        <v>-3.56</v>
+      </c>
+      <c r="I236">
+        <v>-5.445</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>0.04</v>
+      </c>
+      <c r="M236">
+        <v>1.2</v>
+      </c>
+      <c r="N236">
+        <v>1.4</v>
+      </c>
+      <c r="O236">
+        <v>83</v>
+      </c>
+      <c r="P236">
+        <v>0.19</v>
+      </c>
+      <c r="Q236">
+        <v>0.049</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2">
-        <v>45530</v>
+        <v>45593</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8033,22 +8243,49 @@
         </is>
       </c>
       <c r="D237">
-        <v>23.66666666666666</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E237">
-        <v>33.78</v>
+        <v>33.79</v>
       </c>
       <c r="F237">
-        <v>7.87</v>
+        <v>7.84</v>
+      </c>
+      <c r="G237">
+        <v>226.6</v>
+      </c>
+      <c r="H237">
+        <v>-5.82</v>
+      </c>
+      <c r="I237">
+        <v>-5.49</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0.02</v>
+      </c>
+      <c r="M237">
+        <v>1.5</v>
+      </c>
+      <c r="N237">
+        <v>2.2</v>
+      </c>
+      <c r="O237">
+        <v>125</v>
+      </c>
+      <c r="R237">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2">
-        <v>45531</v>
+        <v>45594</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8057,22 +8294,31 @@
         </is>
       </c>
       <c r="D238">
-        <v>24.05555555555556</v>
+        <v>23.27777777777778</v>
       </c>
       <c r="E238">
-        <v>33.32</v>
+        <v>32.13</v>
       </c>
       <c r="F238">
-        <v>7.88</v>
+        <v>7.85</v>
+      </c>
+      <c r="G238">
+        <v>217.5</v>
+      </c>
+      <c r="H238">
+        <v>-5.65</v>
+      </c>
+      <c r="I238">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2">
-        <v>45532</v>
+        <v>45595</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8081,22 +8327,31 @@
         </is>
       </c>
       <c r="D239">
-        <v>24.11111111111111</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="E239">
-        <v>33.44</v>
+        <v>32.36</v>
       </c>
       <c r="F239">
-        <v>7.93</v>
+        <v>7.86</v>
+      </c>
+      <c r="G239">
+        <v>178.1</v>
+      </c>
+      <c r="H239">
+        <v>-3.45</v>
+      </c>
+      <c r="I239">
+        <v>-5.47</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2">
-        <v>45533</v>
+        <v>45596</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8105,22 +8360,31 @@
         </is>
       </c>
       <c r="D240">
-        <v>24.11111111111111</v>
+        <v>23.66666666666666</v>
       </c>
       <c r="E240">
-        <v>33.33</v>
+        <v>32.8</v>
       </c>
       <c r="F240">
-        <v>7.98</v>
+        <v>7.93</v>
+      </c>
+      <c r="G240">
+        <v>200.2</v>
+      </c>
+      <c r="H240">
+        <v>-4.03</v>
+      </c>
+      <c r="I240">
+        <v>-5.42</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2">
-        <v>45534</v>
+        <v>45597</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8129,22 +8393,52 @@
         </is>
       </c>
       <c r="D241">
-        <v>23.66666666666666</v>
+        <v>23.83333333333334</v>
       </c>
       <c r="E241">
-        <v>32.84</v>
+        <v>32.79</v>
       </c>
       <c r="F241">
-        <v>7.87</v>
+        <v>7.86</v>
+      </c>
+      <c r="G241">
+        <v>149.7</v>
+      </c>
+      <c r="H241">
+        <v>-5.74</v>
+      </c>
+      <c r="I241">
+        <v>-5.47</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0.05</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>1.5</v>
+      </c>
+      <c r="O241">
+        <v>110</v>
+      </c>
+      <c r="P241">
+        <v>0.37</v>
+      </c>
+      <c r="Q241">
+        <v>0.095</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2">
-        <v>45539</v>
+        <v>45601</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8153,22 +8447,31 @@
         </is>
       </c>
       <c r="D242">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E242">
-        <v>33.81</v>
+        <v>33.85</v>
       </c>
       <c r="F242">
         <v>7.94</v>
       </c>
+      <c r="G242">
+        <v>196.7</v>
+      </c>
+      <c r="H242">
+        <v>-4.95</v>
+      </c>
+      <c r="I242">
+        <v>-5.48</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2">
-        <v>45540</v>
+        <v>45602</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8177,22 +8480,31 @@
         </is>
       </c>
       <c r="D243">
-        <v>24.05555555555556</v>
+        <v>24.19444444444444</v>
       </c>
       <c r="E243">
-        <v>33.99</v>
+        <v>33.73999999999999</v>
       </c>
       <c r="F243">
-        <v>7.97</v>
+        <v>7.895</v>
+      </c>
+      <c r="G243">
+        <v>168.4</v>
+      </c>
+      <c r="H243">
+        <v>-2.545</v>
+      </c>
+      <c r="I243">
+        <v>-5.455</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2">
-        <v>45541</v>
+        <v>45603</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8201,22 +8513,31 @@
         </is>
       </c>
       <c r="D244">
-        <v>24.11111111111111</v>
+        <v>23.94444444444444</v>
       </c>
       <c r="E244">
-        <v>34.1</v>
+        <v>33.96</v>
       </c>
       <c r="F244">
         <v>7.91</v>
       </c>
+      <c r="G244">
+        <v>223.5</v>
+      </c>
+      <c r="H244">
+        <v>-3.36</v>
+      </c>
+      <c r="I244">
+        <v>-5.43</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2">
-        <v>45544</v>
+        <v>45604</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 3  Control</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8225,43 +8546,52 @@
         </is>
       </c>
       <c r="D245">
-        <v>23.33333333333333</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E245">
-        <v>34.81</v>
+        <v>33.41</v>
       </c>
       <c r="F245">
-        <v>7.87</v>
+        <v>7.86</v>
+      </c>
+      <c r="G245">
+        <v>154.1</v>
+      </c>
+      <c r="H245">
+        <v>-4.5</v>
+      </c>
+      <c r="I245">
+        <v>-5.46</v>
       </c>
       <c r="K245">
         <v>0</v>
       </c>
       <c r="L245">
-        <v>0.3</v>
+        <v>0.04</v>
       </c>
       <c r="M245">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="N245">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="O245">
-        <v>95</v>
-      </c>
-      <c r="R245">
-        <v>0</v>
-      </c>
-      <c r="S245">
-        <v>338</v>
+        <v>115</v>
+      </c>
+      <c r="P245">
+        <v>0.37</v>
+      </c>
+      <c r="Q245">
+        <v>0.04</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2">
-        <v>45545</v>
+        <v>45608</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8270,22 +8600,31 @@
         </is>
       </c>
       <c r="D246">
-        <v>23.72222222222222</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E246">
-        <v>33.98</v>
+        <v>34.33</v>
       </c>
       <c r="F246">
-        <v>7.9</v>
+        <v>7.96</v>
+      </c>
+      <c r="G246">
+        <v>193.1</v>
+      </c>
+      <c r="H246">
+        <v>-0.08</v>
+      </c>
+      <c r="I246">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2">
-        <v>45546</v>
+        <v>45609</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -8294,22 +8633,31 @@
         </is>
       </c>
       <c r="D247">
-        <v>24.05555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E247">
-        <v>34.16</v>
+        <v>34.04</v>
       </c>
       <c r="F247">
-        <v>7.9</v>
+        <v>7.95</v>
+      </c>
+      <c r="G247">
+        <v>146.4</v>
+      </c>
+      <c r="H247">
+        <v>-0.09</v>
+      </c>
+      <c r="I247">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2">
-        <v>45548</v>
+        <v>45610</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8318,43 +8666,31 @@
         </is>
       </c>
       <c r="D248">
-        <v>24.05555555555556</v>
+        <v>23.94444444444444</v>
       </c>
       <c r="E248">
-        <v>34.34</v>
+        <v>33.95</v>
       </c>
       <c r="F248">
-        <v>7.88</v>
-      </c>
-      <c r="K248">
-        <v>0</v>
-      </c>
-      <c r="L248">
-        <v>0.05</v>
-      </c>
-      <c r="M248">
-        <v>1.9</v>
-      </c>
-      <c r="N248">
-        <v>3.2</v>
-      </c>
-      <c r="O248">
-        <v>97</v>
-      </c>
-      <c r="P248">
-        <v>0.12</v>
-      </c>
-      <c r="Q248">
-        <v>0.025</v>
+        <v>7.92</v>
+      </c>
+      <c r="G248">
+        <v>185</v>
+      </c>
+      <c r="H248">
+        <v>0.01</v>
+      </c>
+      <c r="I248">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2">
-        <v>45551</v>
+        <v>45611</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8363,43 +8699,52 @@
         </is>
       </c>
       <c r="D249">
-        <v>23.83333333333334</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E249">
-        <v>34.39</v>
+        <v>33.84</v>
       </c>
       <c r="F249">
         <v>7.88</v>
       </c>
+      <c r="G249">
+        <v>112.1</v>
+      </c>
+      <c r="H249">
+        <v>-0.09</v>
+      </c>
+      <c r="I249">
+        <v>-0.62</v>
+      </c>
       <c r="K249">
         <v>0</v>
       </c>
       <c r="L249">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="M249">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="N249">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O249">
-        <v>96</v>
-      </c>
-      <c r="R249">
-        <v>0</v>
-      </c>
-      <c r="S249">
-        <v>361</v>
+        <v>91</v>
+      </c>
+      <c r="P249">
+        <v>0.52</v>
+      </c>
+      <c r="Q249">
+        <v>0.042</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2">
-        <v>45552</v>
+        <v>45614</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8408,22 +8753,55 @@
         </is>
       </c>
       <c r="D250">
-        <v>23.55555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E250">
-        <v>34.08</v>
+        <v>35</v>
       </c>
       <c r="F250">
-        <v>7.94</v>
+        <v>7.85</v>
+      </c>
+      <c r="G250">
+        <v>164.4</v>
+      </c>
+      <c r="H250">
+        <v>-0.08</v>
+      </c>
+      <c r="I250">
+        <v>-0.62</v>
+      </c>
+      <c r="J250">
+        <v>1.7712</v>
+      </c>
+      <c r="K250">
+        <v>0</v>
+      </c>
+      <c r="L250">
+        <v>0.43</v>
+      </c>
+      <c r="M250">
+        <v>1.2</v>
+      </c>
+      <c r="N250">
+        <v>1.3</v>
+      </c>
+      <c r="O250">
+        <v>91</v>
+      </c>
+      <c r="R250">
+        <v>0</v>
+      </c>
+      <c r="S250">
+        <v>360</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2">
-        <v>45553</v>
+        <v>45616</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8432,22 +8810,31 @@
         </is>
       </c>
       <c r="D251">
-        <v>24.11111111111111</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="E251">
-        <v>34.35</v>
+        <v>33.31</v>
       </c>
       <c r="F251">
-        <v>7.93</v>
+        <v>7.87</v>
+      </c>
+      <c r="G251">
+        <v>150</v>
+      </c>
+      <c r="H251">
+        <v>-0.1</v>
+      </c>
+      <c r="I251">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2">
-        <v>45554</v>
+        <v>45617</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8456,22 +8843,31 @@
         </is>
       </c>
       <c r="D252">
-        <v>24.16666666666667</v>
+        <v>21.31481481481481</v>
       </c>
       <c r="E252">
-        <v>34.6</v>
+        <v>21.84333333333333</v>
       </c>
       <c r="F252">
-        <v>7.94</v>
+        <v>7.616666666666666</v>
+      </c>
+      <c r="G252">
+        <v>138.0333333333333</v>
+      </c>
+      <c r="H252">
+        <v>-0.06333333333333334</v>
+      </c>
+      <c r="I252">
+        <v>-0.5733333333333334</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2">
-        <v>45555</v>
+        <v>45618</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8480,52 +8876,52 @@
         </is>
       </c>
       <c r="D253">
-        <v>24.16666666666667</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E253">
-        <v>34.73</v>
+        <v>33.2</v>
       </c>
       <c r="F253">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="G253">
-        <v>162.1</v>
+        <v>142.9</v>
       </c>
       <c r="H253">
-        <v>-3.27</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I253">
-        <v>-1.13</v>
+        <v>-0.51</v>
       </c>
       <c r="K253">
         <v>0</v>
       </c>
       <c r="L253">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M253">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N253">
         <v>2</v>
       </c>
       <c r="O253">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P253">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="Q253">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2">
-        <v>45558</v>
+        <v>45621</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8534,52 +8930,34 @@
         </is>
       </c>
       <c r="D254">
-        <v>23.55555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E254">
-        <v>35.38</v>
+        <v>33.46</v>
       </c>
       <c r="F254">
-        <v>7.88</v>
+        <v>7.9</v>
       </c>
       <c r="G254">
-        <v>184.2</v>
+        <v>174.5</v>
       </c>
       <c r="H254">
-        <v>-4.44</v>
+        <v>-0.08</v>
       </c>
       <c r="I254">
-        <v>-1.24</v>
-      </c>
-      <c r="K254">
-        <v>0</v>
-      </c>
-      <c r="L254">
-        <v>0.04</v>
-      </c>
-      <c r="M254">
-        <v>1.5</v>
-      </c>
-      <c r="N254">
-        <v>2.1</v>
-      </c>
-      <c r="O254">
-        <v>190</v>
-      </c>
-      <c r="R254">
-        <v>0</v>
-      </c>
-      <c r="S254">
-        <v>356</v>
+        <v>-0.63</v>
+      </c>
+      <c r="J254">
+        <v>1.6848</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2">
-        <v>45559</v>
+        <v>45622</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8588,31 +8966,31 @@
         </is>
       </c>
       <c r="D255">
-        <v>24.05555555555556</v>
+        <v>24</v>
       </c>
       <c r="E255">
-        <v>34.27</v>
+        <v>33.28</v>
       </c>
       <c r="F255">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="G255">
-        <v>229.7</v>
+        <v>210.9</v>
       </c>
       <c r="H255">
-        <v>-4.22</v>
+        <v>-0.09</v>
       </c>
       <c r="I255">
-        <v>-1.21</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2">
-        <v>45560</v>
+        <v>45623</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8624,28 +9002,49 @@
         <v>24.05555555555556</v>
       </c>
       <c r="E256">
-        <v>33.84</v>
+        <v>33.21</v>
       </c>
       <c r="F256">
-        <v>7.92</v>
+        <v>7.88</v>
       </c>
       <c r="G256">
-        <v>174.6</v>
+        <v>186.1</v>
       </c>
       <c r="H256">
-        <v>-4.34</v>
+        <v>-0.1</v>
       </c>
       <c r="I256">
-        <v>-1.24</v>
+        <v>-0.61</v>
+      </c>
+      <c r="K256">
+        <v>0</v>
+      </c>
+      <c r="L256">
+        <v>0.02</v>
+      </c>
+      <c r="M256">
+        <v>1.5</v>
+      </c>
+      <c r="N256">
+        <v>2.2</v>
+      </c>
+      <c r="O256">
+        <v>82</v>
+      </c>
+      <c r="P256">
+        <v>0.83</v>
+      </c>
+      <c r="Q256">
+        <v>0.038</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2">
-        <v>45561</v>
+        <v>45628</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8654,31 +9053,52 @@
         </is>
       </c>
       <c r="D257">
-        <v>24.16666666666667</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E257">
-        <v>33.71</v>
+        <v>34.72</v>
       </c>
       <c r="F257">
-        <v>7.94</v>
+        <v>7.93</v>
       </c>
       <c r="G257">
-        <v>185.5</v>
+        <v>172.4</v>
       </c>
       <c r="H257">
-        <v>-2.56</v>
+        <v>1.28</v>
       </c>
       <c r="I257">
-        <v>-1.19</v>
+        <v>2.95</v>
+      </c>
+      <c r="J257">
+        <v>2.7216</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M257">
+        <v>1.3</v>
+      </c>
+      <c r="N257">
+        <v>2.2</v>
+      </c>
+      <c r="O257">
+        <v>115</v>
+      </c>
+      <c r="R257">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2">
-        <v>45562</v>
+        <v>45630</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8687,52 +9107,31 @@
         </is>
       </c>
       <c r="D258">
-        <v>24.05555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E258">
-        <v>33.32</v>
+        <v>34.23</v>
       </c>
       <c r="F258">
-        <v>7.915</v>
+        <v>7.87</v>
       </c>
       <c r="G258">
-        <v>164.35</v>
+        <v>163</v>
       </c>
       <c r="H258">
-        <v>-4.415</v>
+        <v>0.84</v>
       </c>
       <c r="I258">
-        <v>-1.27</v>
-      </c>
-      <c r="K258">
-        <v>0</v>
-      </c>
-      <c r="L258">
-        <v>0</v>
-      </c>
-      <c r="M258">
-        <v>1.3</v>
-      </c>
-      <c r="N258">
-        <v>1.8</v>
-      </c>
-      <c r="O258">
-        <v>94</v>
-      </c>
-      <c r="P258">
-        <v>0.17</v>
-      </c>
-      <c r="Q258">
-        <v>0.016</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2">
-        <v>45565</v>
+        <v>45631</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8741,52 +9140,31 @@
         </is>
       </c>
       <c r="D259">
-        <v>24.05555555555556</v>
+        <v>24</v>
       </c>
       <c r="E259">
-        <v>34.17</v>
+        <v>33.97</v>
       </c>
       <c r="F259">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
       <c r="G259">
-        <v>169.9</v>
+        <v>195.4</v>
       </c>
       <c r="H259">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="I259">
-        <v>-1.15</v>
-      </c>
-      <c r="J259">
-        <v>2.9376</v>
-      </c>
-      <c r="K259">
-        <v>0</v>
-      </c>
-      <c r="L259">
-        <v>0.11</v>
-      </c>
-      <c r="M259">
-        <v>1.5</v>
-      </c>
-      <c r="N259">
-        <v>2.2</v>
-      </c>
-      <c r="O259">
-        <v>151</v>
-      </c>
-      <c r="R259">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2">
-        <v>45566</v>
+        <v>45632</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8795,31 +9173,52 @@
         </is>
       </c>
       <c r="D260">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E260">
-        <v>34.08</v>
+        <v>34.23</v>
       </c>
       <c r="F260">
-        <v>7.96</v>
+        <v>7.85</v>
       </c>
       <c r="G260">
-        <v>199.7</v>
+        <v>154.9</v>
       </c>
       <c r="H260">
-        <v>-4.72</v>
+        <v>0.29</v>
       </c>
       <c r="I260">
-        <v>-1.26</v>
+        <v>-0.25</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0.02</v>
+      </c>
+      <c r="M260">
+        <v>1</v>
+      </c>
+      <c r="N260">
+        <v>1.8</v>
+      </c>
+      <c r="O260">
+        <v>75</v>
+      </c>
+      <c r="P260">
+        <v>1.41</v>
+      </c>
+      <c r="Q260">
+        <v>0.013</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2">
-        <v>45567</v>
+        <v>45636</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8828,31 +9227,31 @@
         </is>
       </c>
       <c r="D261">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E261">
-        <v>34.32</v>
+        <v>34.97</v>
       </c>
       <c r="F261">
-        <v>7.95</v>
+        <v>7.84</v>
       </c>
       <c r="G261">
-        <v>168.3</v>
+        <v>113.2</v>
       </c>
       <c r="H261">
-        <v>-4.33</v>
+        <v>-0.49</v>
       </c>
       <c r="I261">
-        <v>-1.26</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2">
-        <v>45568</v>
+        <v>45638</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8861,31 +9260,31 @@
         </is>
       </c>
       <c r="D262">
-        <v>24.05555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E262">
-        <v>33.93</v>
+        <v>33.77</v>
       </c>
       <c r="F262">
-        <v>8.02</v>
+        <v>7.87</v>
       </c>
       <c r="G262">
-        <v>153.7</v>
+        <v>197.1</v>
       </c>
       <c r="H262">
-        <v>-1.41</v>
+        <v>-0.53</v>
       </c>
       <c r="I262">
-        <v>-1.06</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2">
-        <v>45569</v>
+        <v>45643</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8897,49 +9296,28 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E263">
-        <v>34.38</v>
+        <v>33.75</v>
       </c>
       <c r="F263">
-        <v>7.84</v>
+        <v>7.88</v>
       </c>
       <c r="G263">
-        <v>159.2</v>
+        <v>173.9</v>
       </c>
       <c r="H263">
-        <v>-5.9</v>
+        <v>-0.52</v>
       </c>
       <c r="I263">
-        <v>-1.3</v>
-      </c>
-      <c r="K263">
-        <v>0</v>
-      </c>
-      <c r="L263">
-        <v>0</v>
-      </c>
-      <c r="M263">
-        <v>1.5</v>
-      </c>
-      <c r="N263">
-        <v>2.1</v>
-      </c>
-      <c r="O263">
-        <v>90</v>
-      </c>
-      <c r="P263">
-        <v>0.2</v>
-      </c>
-      <c r="Q263">
-        <v>0.014</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2">
-        <v>45572</v>
+        <v>45646</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 2  Control</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8948,52 +9326,31 @@
         </is>
       </c>
       <c r="D264">
-        <v>24.05555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E264">
-        <v>34.91</v>
+        <v>34.24</v>
       </c>
       <c r="F264">
-        <v>7.82</v>
+        <v>7.9</v>
       </c>
       <c r="G264">
-        <v>165.6</v>
+        <v>153.2</v>
       </c>
       <c r="H264">
-        <v>-4.85</v>
+        <v>-0.46</v>
       </c>
       <c r="I264">
-        <v>-5.45</v>
-      </c>
-      <c r="J264">
-        <v>2.8944</v>
-      </c>
-      <c r="K264">
-        <v>0</v>
-      </c>
-      <c r="L264">
-        <v>0.03</v>
-      </c>
-      <c r="M264">
-        <v>1.3</v>
-      </c>
-      <c r="N264">
-        <v>2.1</v>
-      </c>
-      <c r="O264">
-        <v>82</v>
-      </c>
-      <c r="R264">
-        <v>0</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2">
-        <v>45573</v>
+        <v>45649</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9002,31 +9359,31 @@
         </is>
       </c>
       <c r="D265">
-        <v>24</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E265">
-        <v>34.57</v>
+        <v>35.14</v>
       </c>
       <c r="F265">
-        <v>7.95</v>
+        <v>7.96</v>
       </c>
       <c r="G265">
-        <v>149.1</v>
+        <v>175.7</v>
       </c>
       <c r="H265">
-        <v>-3.95</v>
+        <v>0.61</v>
       </c>
       <c r="I265">
-        <v>-5.46</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2">
-        <v>45574</v>
+        <v>45656</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9038,28 +9395,28 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E266">
-        <v>34.78</v>
+        <v>35.46</v>
       </c>
       <c r="F266">
-        <v>7.9</v>
+        <v>7.98</v>
       </c>
       <c r="G266">
-        <v>174.5</v>
+        <v>142</v>
       </c>
       <c r="H266">
-        <v>-3.97</v>
+        <v>-0.53</v>
       </c>
       <c r="I266">
-        <v>-5.48</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2">
-        <v>45575</v>
+        <v>45664</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9068,31 +9425,31 @@
         </is>
       </c>
       <c r="D267">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E267">
-        <v>34.91</v>
+        <v>35.14</v>
       </c>
       <c r="F267">
-        <v>7.93</v>
+        <v>7.88</v>
       </c>
       <c r="G267">
         <v>145.4</v>
       </c>
       <c r="H267">
-        <v>-4.12</v>
+        <v>-0.31</v>
       </c>
       <c r="I267">
-        <v>-5.45</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2">
-        <v>45576</v>
+        <v>45667</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9101,52 +9458,52 @@
         </is>
       </c>
       <c r="D268">
-        <v>24</v>
+        <v>24.19444444444444</v>
       </c>
       <c r="E268">
-        <v>34.85</v>
+        <v>35.735</v>
       </c>
       <c r="F268">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="G268">
-        <v>158.8</v>
+        <v>252.95</v>
       </c>
       <c r="H268">
-        <v>-6.04</v>
+        <v>-0.42</v>
       </c>
       <c r="I268">
-        <v>-5.45</v>
+        <v>-3.605</v>
       </c>
       <c r="K268">
         <v>0</v>
       </c>
       <c r="L268">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="M268">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="N268">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="O268">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="P268">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="Q268">
-        <v>0.013</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2">
-        <v>45579</v>
+        <v>45670</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9158,49 +9515,49 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E269">
-        <v>34.79</v>
+        <v>36.35</v>
       </c>
       <c r="F269">
-        <v>7.82</v>
+        <v>7.88</v>
       </c>
       <c r="G269">
-        <v>158.2</v>
+        <v>227.7</v>
       </c>
       <c r="H269">
-        <v>-5.87</v>
+        <v>-0.31</v>
       </c>
       <c r="I269">
-        <v>-5.46</v>
-      </c>
-      <c r="J269">
-        <v>0.864</v>
+        <v>-2.99</v>
       </c>
       <c r="K269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L269">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M269">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N269">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="O269">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="R269">
-        <v>0.01</v>
+        <v>0</v>
+      </c>
+      <c r="S269">
+        <v>376</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2">
-        <v>45580</v>
+        <v>45671</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9212,28 +9569,28 @@
         <v>24.05555555555556</v>
       </c>
       <c r="E270">
-        <v>34.51</v>
+        <v>35.04</v>
       </c>
       <c r="F270">
-        <v>7.98</v>
+        <v>7.82</v>
       </c>
       <c r="G270">
-        <v>156.8</v>
+        <v>241.1</v>
       </c>
       <c r="H270">
-        <v>-6.03</v>
+        <v>-0.32</v>
       </c>
       <c r="I270">
-        <v>-5.47</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2">
-        <v>45581</v>
+        <v>45672</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9242,31 +9599,31 @@
         </is>
       </c>
       <c r="D271">
-        <v>24.05555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E271">
-        <v>34.76</v>
+        <v>35.16</v>
       </c>
       <c r="F271">
-        <v>7.97</v>
+        <v>7.92</v>
       </c>
       <c r="G271">
-        <v>143.6</v>
+        <v>219.1</v>
       </c>
       <c r="H271">
-        <v>-4.27</v>
+        <v>-0.35</v>
       </c>
       <c r="I271">
-        <v>-5.47</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2">
-        <v>45582</v>
+        <v>45674</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9275,31 +9632,52 @@
         </is>
       </c>
       <c r="D272">
-        <v>24.11111111111111</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E272">
-        <v>34.97</v>
+        <v>35.19</v>
       </c>
       <c r="F272">
-        <v>7.92</v>
+        <v>7.88</v>
       </c>
       <c r="G272">
-        <v>167.4</v>
+        <v>199.4</v>
       </c>
       <c r="H272">
-        <v>-4.33</v>
+        <v>-0.34</v>
       </c>
       <c r="I272">
-        <v>-5.44</v>
+        <v>-3.03</v>
+      </c>
+      <c r="K272">
+        <v>0</v>
+      </c>
+      <c r="L272">
+        <v>0.04</v>
+      </c>
+      <c r="M272">
+        <v>1.4</v>
+      </c>
+      <c r="N272">
+        <v>2</v>
+      </c>
+      <c r="O272">
+        <v>107</v>
+      </c>
+      <c r="P272">
+        <v>0.36</v>
+      </c>
+      <c r="Q272">
+        <v>0.047</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2">
-        <v>45583</v>
+        <v>45678</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9308,52 +9686,31 @@
         </is>
       </c>
       <c r="D273">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E273">
-        <v>35.08</v>
+        <v>36.93</v>
       </c>
       <c r="F273">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="G273">
-        <v>150.8</v>
+        <v>196.9</v>
       </c>
       <c r="H273">
-        <v>-4.63</v>
+        <v>-0.34</v>
       </c>
       <c r="I273">
-        <v>-5.45</v>
-      </c>
-      <c r="K273">
-        <v>0</v>
-      </c>
-      <c r="L273">
-        <v>0</v>
-      </c>
-      <c r="M273">
-        <v>1.3</v>
-      </c>
-      <c r="N273">
-        <v>1.7</v>
-      </c>
-      <c r="O273">
-        <v>90</v>
-      </c>
-      <c r="P273">
-        <v>1.17</v>
-      </c>
-      <c r="Q273">
-        <v>0.118</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2">
-        <v>45586</v>
+        <v>45680</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9362,49 +9719,31 @@
         </is>
       </c>
       <c r="D274">
-        <v>24.11111111111111</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E274">
-        <v>35.95</v>
+        <v>33.99</v>
       </c>
       <c r="F274">
         <v>7.89</v>
       </c>
       <c r="G274">
-        <v>176.2</v>
+        <v>206.8</v>
       </c>
       <c r="H274">
-        <v>-5.76</v>
+        <v>-0.3</v>
       </c>
       <c r="I274">
-        <v>-5.48</v>
-      </c>
-      <c r="K274">
-        <v>0</v>
-      </c>
-      <c r="L274">
-        <v>0</v>
-      </c>
-      <c r="M274">
-        <v>1.7</v>
-      </c>
-      <c r="N274">
-        <v>2.3</v>
-      </c>
-      <c r="O274">
-        <v>88</v>
-      </c>
-      <c r="R274">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2">
-        <v>45587</v>
+        <v>45681</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -9413,31 +9752,52 @@
         </is>
       </c>
       <c r="D275">
-        <v>24.16666666666667</v>
+        <v>23.94444444444444</v>
       </c>
       <c r="E275">
-        <v>34.91</v>
+        <v>34.26</v>
       </c>
       <c r="F275">
-        <v>7.96</v>
+        <v>7.89</v>
       </c>
       <c r="G275">
-        <v>201.5</v>
+        <v>211</v>
       </c>
       <c r="H275">
-        <v>-4.85</v>
+        <v>-0.36</v>
       </c>
       <c r="I275">
-        <v>-5.47</v>
+        <v>-2.9</v>
+      </c>
+      <c r="K275">
+        <v>0</v>
+      </c>
+      <c r="L275">
+        <v>0.03</v>
+      </c>
+      <c r="M275">
+        <v>1.6</v>
+      </c>
+      <c r="N275">
+        <v>2.5</v>
+      </c>
+      <c r="O275">
+        <v>108</v>
+      </c>
+      <c r="P275">
+        <v>0.72</v>
+      </c>
+      <c r="Q275">
+        <v>0.02</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2">
-        <v>45588</v>
+        <v>45684</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -9446,31 +9806,52 @@
         </is>
       </c>
       <c r="D276">
-        <v>24.16666666666667</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E276">
-        <v>35.21</v>
+        <v>35.25</v>
       </c>
       <c r="F276">
-        <v>7.98</v>
+        <v>7.86</v>
       </c>
       <c r="G276">
-        <v>201.3</v>
+        <v>224.9</v>
       </c>
       <c r="H276">
-        <v>-5.17</v>
+        <v>-0.34</v>
       </c>
       <c r="I276">
-        <v>-5.46</v>
+        <v>-2.93</v>
+      </c>
+      <c r="K276">
+        <v>0</v>
+      </c>
+      <c r="L276">
+        <v>0.02</v>
+      </c>
+      <c r="M276">
+        <v>1.2</v>
+      </c>
+      <c r="N276">
+        <v>1.9</v>
+      </c>
+      <c r="O276">
+        <v>94</v>
+      </c>
+      <c r="R276">
+        <v>0</v>
+      </c>
+      <c r="S276">
+        <v>348</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2">
-        <v>45589</v>
+        <v>45685</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -9482,28 +9863,28 @@
         <v>24.11111111111111</v>
       </c>
       <c r="E277">
-        <v>35.5</v>
+        <v>34.71</v>
       </c>
       <c r="F277">
-        <v>7.99</v>
+        <v>7.87</v>
       </c>
       <c r="G277">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="H277">
-        <v>-3.68</v>
+        <v>-0.35</v>
       </c>
       <c r="I277">
-        <v>-5.44</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2">
-        <v>45590</v>
+        <v>45686</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9512,52 +9893,31 @@
         </is>
       </c>
       <c r="D278">
-        <v>24.13888888888889</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E278">
-        <v>34.19499999999999</v>
+        <v>35.05</v>
       </c>
       <c r="F278">
-        <v>7.91</v>
+        <v>7.89</v>
       </c>
       <c r="G278">
-        <v>245.75</v>
+        <v>172</v>
       </c>
       <c r="H278">
-        <v>-3.56</v>
+        <v>-0.36</v>
       </c>
       <c r="I278">
-        <v>-5.445</v>
-      </c>
-      <c r="K278">
-        <v>0</v>
-      </c>
-      <c r="L278">
-        <v>0.04</v>
-      </c>
-      <c r="M278">
-        <v>1.2</v>
-      </c>
-      <c r="N278">
-        <v>1.4</v>
-      </c>
-      <c r="O278">
-        <v>83</v>
-      </c>
-      <c r="P278">
-        <v>0.19</v>
-      </c>
-      <c r="Q278">
-        <v>0.049</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2">
-        <v>45593</v>
+        <v>45687</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -9569,46 +9929,28 @@
         <v>24.16666666666667</v>
       </c>
       <c r="E279">
-        <v>33.79</v>
+        <v>35.14</v>
       </c>
       <c r="F279">
-        <v>7.84</v>
+        <v>7.9</v>
       </c>
       <c r="G279">
-        <v>226.6</v>
+        <v>188</v>
       </c>
       <c r="H279">
-        <v>-5.82</v>
+        <v>-0.34</v>
       </c>
       <c r="I279">
-        <v>-5.49</v>
-      </c>
-      <c r="K279">
-        <v>0</v>
-      </c>
-      <c r="L279">
-        <v>0.02</v>
-      </c>
-      <c r="M279">
-        <v>1.5</v>
-      </c>
-      <c r="N279">
-        <v>2.2</v>
-      </c>
-      <c r="O279">
-        <v>125</v>
-      </c>
-      <c r="R279">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2">
-        <v>45594</v>
+        <v>45688</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -9617,31 +9959,52 @@
         </is>
       </c>
       <c r="D280">
-        <v>23.27777777777778</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E280">
-        <v>32.13</v>
+        <v>34.74</v>
       </c>
       <c r="F280">
-        <v>7.85</v>
+        <v>7.8</v>
       </c>
       <c r="G280">
-        <v>217.5</v>
+        <v>208.3</v>
       </c>
       <c r="H280">
-        <v>-5.65</v>
+        <v>-0.32</v>
       </c>
       <c r="I280">
-        <v>-5.47</v>
+        <v>-2.69</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0.02</v>
+      </c>
+      <c r="M280">
+        <v>1.4</v>
+      </c>
+      <c r="N280">
+        <v>2.1</v>
+      </c>
+      <c r="O280">
+        <v>100</v>
+      </c>
+      <c r="P280">
+        <v>0.92</v>
+      </c>
+      <c r="Q280">
+        <v>0.035</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2">
-        <v>45595</v>
+        <v>45691</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBR 4  Control</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9650,31 +10013,55 @@
         </is>
       </c>
       <c r="D281">
-        <v>23.16666666666667</v>
+        <v>23.94444444444444</v>
       </c>
       <c r="E281">
-        <v>32.36</v>
+        <v>28.97</v>
       </c>
       <c r="F281">
-        <v>7.86</v>
+        <v>7.85</v>
       </c>
       <c r="G281">
-        <v>178.1</v>
+        <v>209.8</v>
       </c>
       <c r="H281">
-        <v>-3.45</v>
+        <v>-0.25</v>
       </c>
       <c r="I281">
-        <v>-5.47</v>
+        <v>-1.26</v>
+      </c>
+      <c r="J281">
+        <v>3.024</v>
+      </c>
+      <c r="K281">
+        <v>9</v>
+      </c>
+      <c r="L281">
+        <v>0.01</v>
+      </c>
+      <c r="M281">
+        <v>1.2</v>
+      </c>
+      <c r="N281">
+        <v>1.4</v>
+      </c>
+      <c r="O281">
+        <v>92</v>
+      </c>
+      <c r="R281">
+        <v>0.03</v>
+      </c>
+      <c r="S281">
+        <v>269</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2">
-        <v>45596</v>
+        <v>45692</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9683,31 +10070,31 @@
         </is>
       </c>
       <c r="D282">
-        <v>23.66666666666666</v>
+        <v>20.22222222222222</v>
       </c>
       <c r="E282">
-        <v>32.8</v>
+        <v>29.14</v>
       </c>
       <c r="F282">
-        <v>7.93</v>
+        <v>7.91</v>
       </c>
       <c r="G282">
-        <v>200.2</v>
+        <v>194.9</v>
       </c>
       <c r="H282">
-        <v>-4.03</v>
+        <v>-0.38</v>
       </c>
       <c r="I282">
-        <v>-5.42</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2">
-        <v>45597</v>
+        <v>45693</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -9716,52 +10103,31 @@
         </is>
       </c>
       <c r="D283">
-        <v>23.83333333333334</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="E283">
-        <v>32.79</v>
+        <v>29.2</v>
       </c>
       <c r="F283">
-        <v>7.86</v>
+        <v>7.89</v>
       </c>
       <c r="G283">
-        <v>149.7</v>
+        <v>190.3</v>
       </c>
       <c r="H283">
-        <v>-5.74</v>
+        <v>-0.35</v>
       </c>
       <c r="I283">
-        <v>-5.47</v>
-      </c>
-      <c r="K283">
-        <v>0</v>
-      </c>
-      <c r="L283">
-        <v>0.05</v>
-      </c>
-      <c r="M283">
-        <v>1</v>
-      </c>
-      <c r="N283">
-        <v>1.5</v>
-      </c>
-      <c r="O283">
-        <v>110</v>
-      </c>
-      <c r="P283">
-        <v>0.37</v>
-      </c>
-      <c r="Q283">
-        <v>0.095</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2">
-        <v>45601</v>
+        <v>45694</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9770,31 +10136,31 @@
         </is>
       </c>
       <c r="D284">
-        <v>24.16666666666667</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E284">
-        <v>33.85</v>
+        <v>28.64</v>
       </c>
       <c r="F284">
-        <v>7.94</v>
+        <v>7.91</v>
       </c>
       <c r="G284">
-        <v>196.7</v>
+        <v>190.9</v>
       </c>
       <c r="H284">
-        <v>-4.95</v>
+        <v>-0.32</v>
       </c>
       <c r="I284">
-        <v>-5.48</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2">
-        <v>45602</v>
+        <v>45695</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9803,31 +10169,52 @@
         </is>
       </c>
       <c r="D285">
-        <v>24.19444444444444</v>
+        <v>24</v>
       </c>
       <c r="E285">
-        <v>33.73999999999999</v>
+        <v>28.98</v>
       </c>
       <c r="F285">
-        <v>7.895</v>
+        <v>7.81</v>
       </c>
       <c r="G285">
-        <v>168.4</v>
+        <v>184.7</v>
       </c>
       <c r="H285">
-        <v>-2.545</v>
+        <v>-0.3</v>
       </c>
       <c r="I285">
-        <v>-5.455</v>
+        <v>-2.58</v>
+      </c>
+      <c r="K285">
+        <v>0</v>
+      </c>
+      <c r="L285">
+        <v>0.03</v>
+      </c>
+      <c r="M285">
+        <v>1.1</v>
+      </c>
+      <c r="N285">
+        <v>1.8</v>
+      </c>
+      <c r="O285">
+        <v>77</v>
+      </c>
+      <c r="P285">
+        <v>0.76</v>
+      </c>
+      <c r="Q285">
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2">
-        <v>45603</v>
+        <v>45698</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9836,31 +10223,52 @@
         </is>
       </c>
       <c r="D286">
-        <v>23.94444444444444</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E286">
-        <v>33.96</v>
+        <v>29.03</v>
       </c>
       <c r="F286">
-        <v>7.91</v>
+        <v>7.83</v>
       </c>
       <c r="G286">
-        <v>223.5</v>
+        <v>236.1</v>
       </c>
       <c r="H286">
-        <v>-3.36</v>
+        <v>-0.13</v>
       </c>
       <c r="I286">
-        <v>-5.43</v>
+        <v>-3.21</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>0.02</v>
+      </c>
+      <c r="M286">
+        <v>1.1</v>
+      </c>
+      <c r="N286">
+        <v>1.8</v>
+      </c>
+      <c r="O286">
+        <v>157</v>
+      </c>
+      <c r="R286">
+        <v>0</v>
+      </c>
+      <c r="S286">
+        <v>290</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2">
-        <v>45604</v>
+        <v>45699</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9869,52 +10277,31 @@
         </is>
       </c>
       <c r="D287">
-        <v>24.05555555555556</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="E287">
-        <v>33.41</v>
+        <v>29.1</v>
       </c>
       <c r="F287">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="G287">
-        <v>154.1</v>
+        <v>191.5</v>
       </c>
       <c r="H287">
-        <v>-4.5</v>
+        <v>-0.13</v>
       </c>
       <c r="I287">
-        <v>-5.46</v>
-      </c>
-      <c r="K287">
-        <v>0</v>
-      </c>
-      <c r="L287">
-        <v>0.04</v>
-      </c>
-      <c r="M287">
-        <v>0.9</v>
-      </c>
-      <c r="N287">
-        <v>1.6</v>
-      </c>
-      <c r="O287">
-        <v>115</v>
-      </c>
-      <c r="P287">
-        <v>0.37</v>
-      </c>
-      <c r="Q287">
-        <v>0.04</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2">
-        <v>45608</v>
+        <v>45700</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9923,31 +10310,31 @@
         </is>
       </c>
       <c r="D288">
-        <v>24.05555555555556</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E288">
-        <v>34.33</v>
+        <v>31.17</v>
       </c>
       <c r="F288">
-        <v>7.96</v>
+        <v>7.81</v>
       </c>
       <c r="G288">
-        <v>193.1</v>
+        <v>228.8</v>
       </c>
       <c r="H288">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I288">
-        <v>-0.58</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2">
-        <v>45609</v>
+        <v>45701</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9956,31 +10343,31 @@
         </is>
       </c>
       <c r="D289">
-        <v>24.16666666666667</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="E289">
-        <v>34.04</v>
+        <v>31.57</v>
       </c>
       <c r="F289">
-        <v>7.95</v>
+        <v>7.82</v>
       </c>
       <c r="G289">
-        <v>146.4</v>
+        <v>190.2</v>
       </c>
       <c r="H289">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="I289">
-        <v>-0.61</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2">
-        <v>45610</v>
+        <v>45702</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9989,31 +10376,52 @@
         </is>
       </c>
       <c r="D290">
-        <v>23.94444444444444</v>
+        <v>27.73015873015873</v>
       </c>
       <c r="E290">
-        <v>33.95</v>
+        <v>32.01142857142857</v>
       </c>
       <c r="F290">
-        <v>7.92</v>
+        <v>7.858571428571429</v>
       </c>
       <c r="G290">
-        <v>185</v>
+        <v>182.0714285714286</v>
       </c>
       <c r="H290">
-        <v>0.01</v>
+        <v>-0.1228571428571429</v>
       </c>
       <c r="I290">
-        <v>-0.38</v>
+        <v>-3.215714285714286</v>
+      </c>
+      <c r="K290">
+        <v>0</v>
+      </c>
+      <c r="L290">
+        <v>0.03</v>
+      </c>
+      <c r="M290">
+        <v>2.1</v>
+      </c>
+      <c r="N290">
+        <v>3.1</v>
+      </c>
+      <c r="O290">
+        <v>109</v>
+      </c>
+      <c r="P290">
+        <v>0.55</v>
+      </c>
+      <c r="Q290">
+        <v>0.007</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2">
-        <v>45611</v>
+        <v>45705</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10022,52 +10430,55 @@
         </is>
       </c>
       <c r="D291">
-        <v>24.16666666666667</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="E291">
-        <v>33.84</v>
+        <v>33.815</v>
       </c>
       <c r="F291">
-        <v>7.88</v>
+        <v>7.83</v>
       </c>
       <c r="G291">
-        <v>112.1</v>
+        <v>205.4</v>
       </c>
       <c r="H291">
-        <v>-0.09</v>
+        <v>-0.135</v>
       </c>
       <c r="I291">
-        <v>-0.62</v>
+        <v>-3.255</v>
+      </c>
+      <c r="J291">
+        <v>2.6784</v>
       </c>
       <c r="K291">
         <v>0</v>
       </c>
       <c r="L291">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M291">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="N291">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O291">
-        <v>91</v>
-      </c>
-      <c r="P291">
-        <v>0.52</v>
-      </c>
-      <c r="Q291">
-        <v>0.042</v>
+        <v>110</v>
+      </c>
+      <c r="R291">
+        <v>0</v>
+      </c>
+      <c r="S291">
+        <v>358</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2">
-        <v>45614</v>
+        <v>45706</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10076,55 +10487,31 @@
         </is>
       </c>
       <c r="D292">
-        <v>24.11111111111111</v>
+        <v>28.05555555555556</v>
       </c>
       <c r="E292">
-        <v>35</v>
+        <v>34.45</v>
       </c>
       <c r="F292">
         <v>7.85</v>
       </c>
       <c r="G292">
-        <v>164.4</v>
+        <v>189.7</v>
       </c>
       <c r="H292">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="I292">
-        <v>-0.62</v>
-      </c>
-      <c r="J292">
-        <v>1.7712</v>
-      </c>
-      <c r="K292">
-        <v>0</v>
-      </c>
-      <c r="L292">
-        <v>0.43</v>
-      </c>
-      <c r="M292">
-        <v>1.2</v>
-      </c>
-      <c r="N292">
-        <v>1.3</v>
-      </c>
-      <c r="O292">
-        <v>91</v>
-      </c>
-      <c r="R292">
-        <v>0</v>
-      </c>
-      <c r="S292">
-        <v>360</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2">
-        <v>45616</v>
+        <v>45707</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10133,31 +10520,31 @@
         </is>
       </c>
       <c r="D293">
-        <v>23.16666666666667</v>
+        <v>28.5</v>
       </c>
       <c r="E293">
-        <v>33.31</v>
+        <v>34.98</v>
       </c>
       <c r="F293">
-        <v>7.87</v>
+        <v>7.86</v>
       </c>
       <c r="G293">
-        <v>150</v>
+        <v>178.9</v>
       </c>
       <c r="H293">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="I293">
-        <v>-0.66</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2">
-        <v>45617</v>
+        <v>45708</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10166,31 +10553,31 @@
         </is>
       </c>
       <c r="D294">
-        <v>21.31481481481481</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="E294">
-        <v>21.84333333333333</v>
+        <v>35.65</v>
       </c>
       <c r="F294">
-        <v>7.616666666666666</v>
+        <v>7.82</v>
       </c>
       <c r="G294">
-        <v>138.0333333333333</v>
+        <v>238.5</v>
       </c>
       <c r="H294">
-        <v>-0.06333333333333334</v>
+        <v>-0.13</v>
       </c>
       <c r="I294">
-        <v>-0.5733333333333334</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2">
-        <v>45618</v>
+        <v>45709</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10199,52 +10586,52 @@
         </is>
       </c>
       <c r="D295">
-        <v>24.05555555555556</v>
+        <v>28.55555555555556</v>
       </c>
       <c r="E295">
-        <v>33.2</v>
+        <v>35.27</v>
       </c>
       <c r="F295">
-        <v>7.86</v>
+        <v>7.81</v>
       </c>
       <c r="G295">
-        <v>142.9</v>
+        <v>172.3</v>
       </c>
       <c r="H295">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="I295">
-        <v>-0.51</v>
+        <v>-3.27</v>
       </c>
       <c r="K295">
         <v>0</v>
       </c>
       <c r="L295">
+        <v>0.09</v>
+      </c>
+      <c r="M295">
+        <v>1.5</v>
+      </c>
+      <c r="N295">
+        <v>2.2</v>
+      </c>
+      <c r="O295">
+        <v>112</v>
+      </c>
+      <c r="P295">
+        <v>1.69</v>
+      </c>
+      <c r="Q295">
         <v>0.02</v>
-      </c>
-      <c r="M295">
-        <v>1.3</v>
-      </c>
-      <c r="N295">
-        <v>2</v>
-      </c>
-      <c r="O295">
-        <v>86</v>
-      </c>
-      <c r="P295">
-        <v>0.62</v>
-      </c>
-      <c r="Q295">
-        <v>0.039</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2">
-        <v>45621</v>
+        <v>45712</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10253,34 +10640,55 @@
         </is>
       </c>
       <c r="D296">
-        <v>24.16666666666667</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="E296">
-        <v>33.46</v>
+        <v>35.94</v>
       </c>
       <c r="F296">
-        <v>7.9</v>
+        <v>7.81</v>
       </c>
       <c r="G296">
-        <v>174.5</v>
+        <v>186.9</v>
       </c>
       <c r="H296">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="I296">
-        <v>-0.63</v>
+        <v>-3.26</v>
       </c>
       <c r="J296">
-        <v>1.6848</v>
+        <v>2.8512</v>
+      </c>
+      <c r="K296">
+        <v>0</v>
+      </c>
+      <c r="L296">
+        <v>0</v>
+      </c>
+      <c r="M296">
+        <v>1.3</v>
+      </c>
+      <c r="N296">
+        <v>1.9</v>
+      </c>
+      <c r="O296">
+        <v>121</v>
+      </c>
+      <c r="R296">
+        <v>0</v>
+      </c>
+      <c r="S296">
+        <v>373</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2">
-        <v>45622</v>
+        <v>45713</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -10289,31 +10697,31 @@
         </is>
       </c>
       <c r="D297">
-        <v>24</v>
+        <v>31.55555555555556</v>
       </c>
       <c r="E297">
-        <v>33.28</v>
+        <v>36.32</v>
       </c>
       <c r="F297">
-        <v>7.9</v>
+        <v>7.83</v>
       </c>
       <c r="G297">
-        <v>210.9</v>
+        <v>234.4</v>
       </c>
       <c r="H297">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="I297">
-        <v>-0.65</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2">
-        <v>45623</v>
+        <v>45714</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -10322,52 +10730,31 @@
         </is>
       </c>
       <c r="D298">
-        <v>24.05555555555556</v>
+        <v>31.88888888888889</v>
       </c>
       <c r="E298">
-        <v>33.21</v>
+        <v>34.17</v>
       </c>
       <c r="F298">
-        <v>7.88</v>
+        <v>7.92</v>
       </c>
       <c r="G298">
-        <v>186.1</v>
+        <v>161</v>
       </c>
       <c r="H298">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="I298">
-        <v>-0.61</v>
-      </c>
-      <c r="K298">
-        <v>0</v>
-      </c>
-      <c r="L298">
-        <v>0.02</v>
-      </c>
-      <c r="M298">
-        <v>1.5</v>
-      </c>
-      <c r="N298">
-        <v>2.2</v>
-      </c>
-      <c r="O298">
-        <v>82</v>
-      </c>
-      <c r="P298">
-        <v>0.83</v>
-      </c>
-      <c r="Q298">
-        <v>0.038</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2">
-        <v>45628</v>
+        <v>45719</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -10376,22 +10763,22 @@
         </is>
       </c>
       <c r="D299">
-        <v>24.11111111111111</v>
+        <v>31.77777777777778</v>
       </c>
       <c r="E299">
-        <v>34.72</v>
+        <v>36.09</v>
       </c>
       <c r="F299">
-        <v>7.93</v>
+        <v>7.85</v>
       </c>
       <c r="G299">
-        <v>172.4</v>
+        <v>176</v>
       </c>
       <c r="H299">
-        <v>1.28</v>
+        <v>-0.11</v>
       </c>
       <c r="I299">
-        <v>2.95</v>
+        <v>-3.17</v>
       </c>
       <c r="J299">
         <v>2.7216</v>
@@ -10400,28 +10787,31 @@
         <v>0</v>
       </c>
       <c r="L299">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M299">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N299">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O299">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="R299">
         <v>0</v>
+      </c>
+      <c r="S299">
+        <v>392</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2">
-        <v>45630</v>
+        <v>45720</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10430,31 +10820,31 @@
         </is>
       </c>
       <c r="D300">
-        <v>24.11111111111111</v>
+        <v>31.88888888888889</v>
       </c>
       <c r="E300">
-        <v>34.23</v>
+        <v>37.04</v>
       </c>
       <c r="F300">
-        <v>7.87</v>
+        <v>7.86</v>
       </c>
       <c r="G300">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H300">
-        <v>0.84</v>
+        <v>-0.1</v>
       </c>
       <c r="I300">
-        <v>0.6899999999999999</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2">
-        <v>45631</v>
+        <v>45721</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -10463,31 +10853,31 @@
         </is>
       </c>
       <c r="D301">
-        <v>24</v>
+        <v>32.05555555555556</v>
       </c>
       <c r="E301">
-        <v>33.97</v>
+        <v>37.92</v>
       </c>
       <c r="F301">
         <v>7.86</v>
       </c>
       <c r="G301">
-        <v>195.4</v>
+        <v>163.9</v>
       </c>
       <c r="H301">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="I301">
-        <v>0.13</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2">
-        <v>45632</v>
+        <v>45722</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10496,52 +10886,31 @@
         </is>
       </c>
       <c r="D302">
-        <v>24.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="E302">
-        <v>34.23</v>
+        <v>36.41</v>
       </c>
       <c r="F302">
-        <v>7.85</v>
+        <v>7.84</v>
       </c>
       <c r="G302">
-        <v>154.9</v>
+        <v>200.2</v>
       </c>
       <c r="H302">
-        <v>0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="I302">
-        <v>-0.25</v>
-      </c>
-      <c r="K302">
-        <v>0</v>
-      </c>
-      <c r="L302">
-        <v>0.02</v>
-      </c>
-      <c r="M302">
-        <v>1</v>
-      </c>
-      <c r="N302">
-        <v>1.8</v>
-      </c>
-      <c r="O302">
-        <v>75</v>
-      </c>
-      <c r="P302">
-        <v>1.41</v>
-      </c>
-      <c r="Q302">
-        <v>0.013</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2">
-        <v>45636</v>
+        <v>45723</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10550,31 +10919,52 @@
         </is>
       </c>
       <c r="D303">
-        <v>24.16666666666667</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E303">
-        <v>34.97</v>
+        <v>34.82</v>
       </c>
       <c r="F303">
         <v>7.84</v>
       </c>
       <c r="G303">
-        <v>113.2</v>
+        <v>163.4</v>
       </c>
       <c r="H303">
-        <v>-0.49</v>
+        <v>-0.12</v>
       </c>
       <c r="I303">
-        <v>-4</v>
+        <v>-3.17</v>
+      </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+      <c r="M303">
+        <v>1.3</v>
+      </c>
+      <c r="N303">
+        <v>1.9</v>
+      </c>
+      <c r="O303">
+        <v>99</v>
+      </c>
+      <c r="P303">
+        <v>0.34</v>
+      </c>
+      <c r="Q303">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2">
-        <v>45638</v>
+        <v>45728</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -10583,31 +10973,31 @@
         </is>
       </c>
       <c r="D304">
-        <v>24.16666666666667</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="E304">
-        <v>33.77</v>
+        <v>34.46</v>
       </c>
       <c r="F304">
-        <v>7.87</v>
+        <v>7.97</v>
       </c>
       <c r="G304">
-        <v>197.1</v>
+        <v>199.7</v>
       </c>
       <c r="H304">
-        <v>-0.53</v>
+        <v>2.65</v>
       </c>
       <c r="I304">
-        <v>-4.06</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2">
-        <v>45643</v>
+        <v>45729</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -10616,31 +11006,31 @@
         </is>
       </c>
       <c r="D305">
-        <v>24.11111111111111</v>
+        <v>24.05555555555556</v>
       </c>
       <c r="E305">
-        <v>33.75</v>
+        <v>34.2</v>
       </c>
       <c r="F305">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="G305">
-        <v>173.9</v>
+        <v>177.5</v>
       </c>
       <c r="H305">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="I305">
-        <v>-4.03</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2">
-        <v>45646</v>
+        <v>45730</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -10649,31 +11039,31 @@
         </is>
       </c>
       <c r="D306">
-        <v>24.16666666666667</v>
+        <v>24.22222222222222</v>
       </c>
       <c r="E306">
-        <v>34.24</v>
+        <v>34.33</v>
       </c>
       <c r="F306">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="G306">
-        <v>153.2</v>
+        <v>175.4</v>
       </c>
       <c r="H306">
-        <v>-0.46</v>
+        <v>4.34</v>
       </c>
       <c r="I306">
-        <v>-3.86</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2">
-        <v>45649</v>
+        <v>45733</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>PBC 3  Control</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -10682,1758 +11072,45 @@
         </is>
       </c>
       <c r="D307">
-        <v>24.05555555555556</v>
+        <v>23.94444444444444</v>
       </c>
       <c r="E307">
-        <v>35.14</v>
+        <v>34.43</v>
       </c>
       <c r="F307">
-        <v>7.96</v>
+        <v>7.92</v>
       </c>
       <c r="G307">
-        <v>175.7</v>
+        <v>155.3</v>
       </c>
       <c r="H307">
-        <v>0.61</v>
+        <v>1.93</v>
       </c>
       <c r="I307">
-        <v>6.79</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2">
-        <v>45656</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D308">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E308">
-        <v>35.46</v>
-      </c>
-      <c r="F308">
-        <v>7.98</v>
-      </c>
-      <c r="G308">
-        <v>142</v>
-      </c>
-      <c r="H308">
-        <v>-0.53</v>
-      </c>
-      <c r="I308">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2">
-        <v>45664</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D309">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="E309">
-        <v>35.14</v>
-      </c>
-      <c r="F309">
-        <v>7.88</v>
-      </c>
-      <c r="G309">
-        <v>145.4</v>
-      </c>
-      <c r="H309">
-        <v>-0.31</v>
-      </c>
-      <c r="I309">
-        <v>-3.73</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2">
-        <v>45667</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D310">
-        <v>24.19444444444444</v>
-      </c>
-      <c r="E310">
-        <v>35.735</v>
-      </c>
-      <c r="F310">
-        <v>7.91</v>
-      </c>
-      <c r="G310">
-        <v>252.95</v>
-      </c>
-      <c r="H310">
-        <v>-0.42</v>
-      </c>
-      <c r="I310">
-        <v>-3.605</v>
-      </c>
-      <c r="K310">
-        <v>0</v>
-      </c>
-      <c r="L310">
-        <v>0.04</v>
-      </c>
-      <c r="M310">
-        <v>1.3</v>
-      </c>
-      <c r="N310">
-        <v>2.2</v>
-      </c>
-      <c r="O310">
-        <v>106</v>
-      </c>
-      <c r="P310">
-        <v>0.42</v>
-      </c>
-      <c r="Q310">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2">
-        <v>45670</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D311">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E311">
-        <v>36.35</v>
-      </c>
-      <c r="F311">
-        <v>7.88</v>
-      </c>
-      <c r="G311">
-        <v>227.7</v>
-      </c>
-      <c r="H311">
-        <v>-0.31</v>
-      </c>
-      <c r="I311">
-        <v>-2.99</v>
-      </c>
-      <c r="K311">
-        <v>0</v>
-      </c>
-      <c r="L311">
+        <v>-3.32</v>
+      </c>
+      <c r="J307">
+        <v>3.2832</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
         <v>0.03</v>
       </c>
-      <c r="M311">
-        <v>1.1</v>
-      </c>
-      <c r="N311">
-        <v>1.7</v>
-      </c>
-      <c r="O311">
-        <v>85</v>
-      </c>
-      <c r="R311">
-        <v>0</v>
-      </c>
-      <c r="S311">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2">
-        <v>45671</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D312">
-        <v>24.05555555555556</v>
-      </c>
-      <c r="E312">
-        <v>35.04</v>
-      </c>
-      <c r="F312">
-        <v>7.82</v>
-      </c>
-      <c r="G312">
-        <v>241.1</v>
-      </c>
-      <c r="H312">
-        <v>-0.32</v>
-      </c>
-      <c r="I312">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2">
-        <v>45672</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D313">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E313">
-        <v>35.16</v>
-      </c>
-      <c r="F313">
-        <v>7.92</v>
-      </c>
-      <c r="G313">
-        <v>219.1</v>
-      </c>
-      <c r="H313">
-        <v>-0.35</v>
-      </c>
-      <c r="I313">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2">
-        <v>45674</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D314">
-        <v>24.22222222222222</v>
-      </c>
-      <c r="E314">
-        <v>35.19</v>
-      </c>
-      <c r="F314">
-        <v>7.88</v>
-      </c>
-      <c r="G314">
-        <v>199.4</v>
-      </c>
-      <c r="H314">
-        <v>-0.34</v>
-      </c>
-      <c r="I314">
-        <v>-3.03</v>
-      </c>
-      <c r="K314">
-        <v>0</v>
-      </c>
-      <c r="L314">
-        <v>0.04</v>
-      </c>
-      <c r="M314">
-        <v>1.4</v>
-      </c>
-      <c r="N314">
-        <v>2</v>
-      </c>
-      <c r="O314">
-        <v>107</v>
-      </c>
-      <c r="P314">
-        <v>0.36</v>
-      </c>
-      <c r="Q314">
-        <v>0.047</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2">
-        <v>45678</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D315">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="E315">
-        <v>36.93</v>
-      </c>
-      <c r="F315">
-        <v>7.9</v>
-      </c>
-      <c r="G315">
-        <v>196.9</v>
-      </c>
-      <c r="H315">
-        <v>-0.34</v>
-      </c>
-      <c r="I315">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2">
-        <v>45680</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D316">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="E316">
-        <v>33.99</v>
-      </c>
-      <c r="F316">
-        <v>7.89</v>
-      </c>
-      <c r="G316">
-        <v>206.8</v>
-      </c>
-      <c r="H316">
-        <v>-0.3</v>
-      </c>
-      <c r="I316">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2">
-        <v>45681</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D317">
-        <v>23.94444444444444</v>
-      </c>
-      <c r="E317">
-        <v>34.26</v>
-      </c>
-      <c r="F317">
-        <v>7.89</v>
-      </c>
-      <c r="G317">
-        <v>211</v>
-      </c>
-      <c r="H317">
-        <v>-0.36</v>
-      </c>
-      <c r="I317">
-        <v>-2.9</v>
-      </c>
-      <c r="K317">
-        <v>0</v>
-      </c>
-      <c r="L317">
-        <v>0.03</v>
-      </c>
-      <c r="M317">
-        <v>1.6</v>
-      </c>
-      <c r="N317">
-        <v>2.5</v>
-      </c>
-      <c r="O317">
-        <v>108</v>
-      </c>
-      <c r="P317">
-        <v>0.72</v>
-      </c>
-      <c r="Q317">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2">
-        <v>45684</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D318">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E318">
-        <v>35.25</v>
-      </c>
-      <c r="F318">
-        <v>7.86</v>
-      </c>
-      <c r="G318">
-        <v>224.9</v>
-      </c>
-      <c r="H318">
-        <v>-0.34</v>
-      </c>
-      <c r="I318">
-        <v>-2.93</v>
-      </c>
-      <c r="K318">
-        <v>0</v>
-      </c>
-      <c r="L318">
-        <v>0.02</v>
-      </c>
-      <c r="M318">
-        <v>1.2</v>
-      </c>
-      <c r="N318">
-        <v>1.9</v>
-      </c>
-      <c r="O318">
-        <v>94</v>
-      </c>
-      <c r="R318">
-        <v>0</v>
-      </c>
-      <c r="S318">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2">
-        <v>45685</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D319">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E319">
-        <v>34.71</v>
-      </c>
-      <c r="F319">
-        <v>7.87</v>
-      </c>
-      <c r="G319">
-        <v>225</v>
-      </c>
-      <c r="H319">
-        <v>-0.35</v>
-      </c>
-      <c r="I319">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2">
-        <v>45686</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D320">
-        <v>24.05555555555556</v>
-      </c>
-      <c r="E320">
-        <v>35.05</v>
-      </c>
-      <c r="F320">
-        <v>7.89</v>
-      </c>
-      <c r="G320">
-        <v>172</v>
-      </c>
-      <c r="H320">
-        <v>-0.36</v>
-      </c>
-      <c r="I320">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2">
-        <v>45687</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D321">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="E321">
-        <v>35.14</v>
-      </c>
-      <c r="F321">
-        <v>7.9</v>
-      </c>
-      <c r="G321">
-        <v>188</v>
-      </c>
-      <c r="H321">
-        <v>-0.34</v>
-      </c>
-      <c r="I321">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2">
-        <v>45688</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D322">
-        <v>24.05555555555556</v>
-      </c>
-      <c r="E322">
-        <v>34.74</v>
-      </c>
-      <c r="F322">
-        <v>7.8</v>
-      </c>
-      <c r="G322">
-        <v>208.3</v>
-      </c>
-      <c r="H322">
-        <v>-0.32</v>
-      </c>
-      <c r="I322">
-        <v>-2.69</v>
-      </c>
-      <c r="K322">
-        <v>0</v>
-      </c>
-      <c r="L322">
-        <v>0.02</v>
-      </c>
-      <c r="M322">
-        <v>1.4</v>
-      </c>
-      <c r="N322">
-        <v>2.1</v>
-      </c>
-      <c r="O322">
-        <v>100</v>
-      </c>
-      <c r="P322">
-        <v>0.92</v>
-      </c>
-      <c r="Q322">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2">
-        <v>45691</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D323">
-        <v>23.94444444444444</v>
-      </c>
-      <c r="E323">
-        <v>28.97</v>
-      </c>
-      <c r="F323">
-        <v>7.85</v>
-      </c>
-      <c r="G323">
-        <v>209.8</v>
-      </c>
-      <c r="H323">
-        <v>-0.25</v>
-      </c>
-      <c r="I323">
-        <v>-1.26</v>
-      </c>
-      <c r="J323">
-        <v>3.024</v>
-      </c>
-      <c r="K323">
-        <v>9</v>
-      </c>
-      <c r="L323">
-        <v>0.01</v>
-      </c>
-      <c r="M323">
-        <v>1.2</v>
-      </c>
-      <c r="N323">
-        <v>1.4</v>
-      </c>
-      <c r="O323">
-        <v>92</v>
-      </c>
-      <c r="R323">
-        <v>0.03</v>
-      </c>
-      <c r="S323">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2">
-        <v>45692</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D324">
-        <v>20.22222222222222</v>
-      </c>
-      <c r="E324">
-        <v>29.14</v>
-      </c>
-      <c r="F324">
-        <v>7.91</v>
-      </c>
-      <c r="G324">
-        <v>194.9</v>
-      </c>
-      <c r="H324">
-        <v>-0.38</v>
-      </c>
-      <c r="I324">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2">
-        <v>45693</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D325">
-        <v>19.16666666666667</v>
-      </c>
-      <c r="E325">
-        <v>29.2</v>
-      </c>
-      <c r="F325">
-        <v>7.89</v>
-      </c>
-      <c r="G325">
-        <v>190.3</v>
-      </c>
-      <c r="H325">
-        <v>-0.35</v>
-      </c>
-      <c r="I325">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2">
-        <v>45694</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D326">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E326">
-        <v>28.64</v>
-      </c>
-      <c r="F326">
-        <v>7.91</v>
-      </c>
-      <c r="G326">
-        <v>190.9</v>
-      </c>
-      <c r="H326">
-        <v>-0.32</v>
-      </c>
-      <c r="I326">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2">
-        <v>45695</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D327">
-        <v>24</v>
-      </c>
-      <c r="E327">
-        <v>28.98</v>
-      </c>
-      <c r="F327">
-        <v>7.81</v>
-      </c>
-      <c r="G327">
-        <v>184.7</v>
-      </c>
-      <c r="H327">
-        <v>-0.3</v>
-      </c>
-      <c r="I327">
-        <v>-2.58</v>
-      </c>
-      <c r="K327">
-        <v>0</v>
-      </c>
-      <c r="L327">
-        <v>0.03</v>
-      </c>
-      <c r="M327">
-        <v>1.1</v>
-      </c>
-      <c r="N327">
-        <v>1.8</v>
-      </c>
-      <c r="O327">
-        <v>77</v>
-      </c>
-      <c r="P327">
-        <v>0.76</v>
-      </c>
-      <c r="Q327">
-        <v>0.008999999999999999</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="2">
-        <v>45698</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D328">
-        <v>24.22222222222222</v>
-      </c>
-      <c r="E328">
-        <v>29.03</v>
-      </c>
-      <c r="F328">
-        <v>7.83</v>
-      </c>
-      <c r="G328">
-        <v>236.1</v>
-      </c>
-      <c r="H328">
-        <v>-0.13</v>
-      </c>
-      <c r="I328">
-        <v>-3.21</v>
-      </c>
-      <c r="K328">
-        <v>0</v>
-      </c>
-      <c r="L328">
-        <v>0.02</v>
-      </c>
-      <c r="M328">
-        <v>1.1</v>
-      </c>
-      <c r="N328">
-        <v>1.8</v>
-      </c>
-      <c r="O328">
-        <v>157</v>
-      </c>
-      <c r="R328">
-        <v>0</v>
-      </c>
-      <c r="S328">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2">
-        <v>45699</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D329">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="E329">
-        <v>29.1</v>
-      </c>
-      <c r="F329">
-        <v>7.87</v>
-      </c>
-      <c r="G329">
-        <v>191.5</v>
-      </c>
-      <c r="H329">
-        <v>-0.13</v>
-      </c>
-      <c r="I329">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="2">
-        <v>45700</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D330">
-        <v>24.16666666666667</v>
-      </c>
-      <c r="E330">
-        <v>31.17</v>
-      </c>
-      <c r="F330">
-        <v>7.81</v>
-      </c>
-      <c r="G330">
-        <v>228.8</v>
-      </c>
-      <c r="H330">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I330">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="2">
-        <v>45701</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D331">
-        <v>26.83333333333333</v>
-      </c>
-      <c r="E331">
-        <v>31.57</v>
-      </c>
-      <c r="F331">
-        <v>7.82</v>
-      </c>
-      <c r="G331">
-        <v>190.2</v>
-      </c>
-      <c r="H331">
-        <v>-0.14</v>
-      </c>
-      <c r="I331">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2">
-        <v>45702</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D332">
-        <v>27.73015873015873</v>
-      </c>
-      <c r="E332">
-        <v>32.01142857142857</v>
-      </c>
-      <c r="F332">
-        <v>7.858571428571429</v>
-      </c>
-      <c r="G332">
-        <v>182.0714285714286</v>
-      </c>
-      <c r="H332">
-        <v>-0.1228571428571429</v>
-      </c>
-      <c r="I332">
-        <v>-3.215714285714286</v>
-      </c>
-      <c r="K332">
-        <v>0</v>
-      </c>
-      <c r="L332">
-        <v>0.03</v>
-      </c>
-      <c r="M332">
-        <v>2.1</v>
-      </c>
-      <c r="N332">
-        <v>3.1</v>
-      </c>
-      <c r="O332">
-        <v>109</v>
-      </c>
-      <c r="P332">
-        <v>0.55</v>
-      </c>
-      <c r="Q332">
-        <v>0.007</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2">
-        <v>45705</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D333">
-        <v>27.66666666666667</v>
-      </c>
-      <c r="E333">
-        <v>33.815</v>
-      </c>
-      <c r="F333">
-        <v>7.83</v>
-      </c>
-      <c r="G333">
-        <v>205.4</v>
-      </c>
-      <c r="H333">
-        <v>-0.135</v>
-      </c>
-      <c r="I333">
-        <v>-3.255</v>
-      </c>
-      <c r="J333">
-        <v>2.6784</v>
-      </c>
-      <c r="K333">
-        <v>0</v>
-      </c>
-      <c r="L333">
-        <v>0</v>
-      </c>
-      <c r="M333">
-        <v>1.1</v>
-      </c>
-      <c r="N333">
-        <v>1.7</v>
-      </c>
-      <c r="O333">
-        <v>110</v>
-      </c>
-      <c r="R333">
-        <v>0</v>
-      </c>
-      <c r="S333">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2">
-        <v>45706</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D334">
-        <v>28.05555555555556</v>
-      </c>
-      <c r="E334">
-        <v>34.45</v>
-      </c>
-      <c r="F334">
-        <v>7.85</v>
-      </c>
-      <c r="G334">
-        <v>189.7</v>
-      </c>
-      <c r="H334">
-        <v>-0.13</v>
-      </c>
-      <c r="I334">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2">
-        <v>45707</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D335">
-        <v>28.5</v>
-      </c>
-      <c r="E335">
-        <v>34.98</v>
-      </c>
-      <c r="F335">
-        <v>7.86</v>
-      </c>
-      <c r="G335">
-        <v>178.9</v>
-      </c>
-      <c r="H335">
-        <v>-0.15</v>
-      </c>
-      <c r="I335">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2">
-        <v>45708</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D336">
-        <v>28.83333333333333</v>
-      </c>
-      <c r="E336">
-        <v>35.65</v>
-      </c>
-      <c r="F336">
-        <v>7.82</v>
-      </c>
-      <c r="G336">
-        <v>238.5</v>
-      </c>
-      <c r="H336">
-        <v>-0.13</v>
-      </c>
-      <c r="I336">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2">
-        <v>45709</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D337">
-        <v>28.55555555555556</v>
-      </c>
-      <c r="E337">
-        <v>35.27</v>
-      </c>
-      <c r="F337">
-        <v>7.81</v>
-      </c>
-      <c r="G337">
-        <v>172.3</v>
-      </c>
-      <c r="H337">
-        <v>-0.14</v>
-      </c>
-      <c r="I337">
-        <v>-3.27</v>
-      </c>
-      <c r="K337">
-        <v>0</v>
-      </c>
-      <c r="L337">
-        <v>0.09</v>
-      </c>
-      <c r="M337">
+      <c r="M307">
         <v>1.5</v>
       </c>
-      <c r="N337">
-        <v>2.2</v>
-      </c>
-      <c r="O337">
-        <v>112</v>
-      </c>
-      <c r="P337">
-        <v>1.69</v>
-      </c>
-      <c r="Q337">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2">
-        <v>45712</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D338">
-        <v>31.11111111111111</v>
-      </c>
-      <c r="E338">
-        <v>35.94</v>
-      </c>
-      <c r="F338">
-        <v>7.81</v>
-      </c>
-      <c r="G338">
-        <v>186.9</v>
-      </c>
-      <c r="H338">
-        <v>-0.14</v>
-      </c>
-      <c r="I338">
-        <v>-3.26</v>
-      </c>
-      <c r="J338">
-        <v>2.8512</v>
-      </c>
-      <c r="K338">
-        <v>0</v>
-      </c>
-      <c r="L338">
-        <v>0</v>
-      </c>
-      <c r="M338">
-        <v>1.3</v>
-      </c>
-      <c r="N338">
-        <v>1.9</v>
-      </c>
-      <c r="O338">
-        <v>121</v>
-      </c>
-      <c r="R338">
-        <v>0</v>
-      </c>
-      <c r="S338">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2">
-        <v>45713</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D339">
-        <v>31.55555555555556</v>
-      </c>
-      <c r="E339">
-        <v>36.32</v>
-      </c>
-      <c r="F339">
-        <v>7.83</v>
-      </c>
-      <c r="G339">
-        <v>234.4</v>
-      </c>
-      <c r="H339">
-        <v>-0.12</v>
-      </c>
-      <c r="I339">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2">
-        <v>45714</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D340">
-        <v>31.88888888888889</v>
-      </c>
-      <c r="E340">
-        <v>34.17</v>
-      </c>
-      <c r="F340">
-        <v>7.92</v>
-      </c>
-      <c r="G340">
-        <v>161</v>
-      </c>
-      <c r="H340">
-        <v>-0.12</v>
-      </c>
-      <c r="I340">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2">
-        <v>45719</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D341">
-        <v>31.77777777777778</v>
-      </c>
-      <c r="E341">
-        <v>36.09</v>
-      </c>
-      <c r="F341">
-        <v>7.85</v>
-      </c>
-      <c r="G341">
-        <v>176</v>
-      </c>
-      <c r="H341">
-        <v>-0.11</v>
-      </c>
-      <c r="I341">
-        <v>-3.17</v>
-      </c>
-      <c r="J341">
-        <v>2.7216</v>
-      </c>
-      <c r="K341">
-        <v>0</v>
-      </c>
-      <c r="L341">
-        <v>0.06</v>
-      </c>
-      <c r="M341">
-        <v>1.4</v>
-      </c>
-      <c r="N341">
-        <v>1.7</v>
-      </c>
-      <c r="O341">
-        <v>164</v>
-      </c>
-      <c r="R341">
-        <v>0</v>
-      </c>
-      <c r="S341">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="2">
-        <v>45720</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D342">
-        <v>31.88888888888889</v>
-      </c>
-      <c r="E342">
-        <v>37.04</v>
-      </c>
-      <c r="F342">
-        <v>7.86</v>
-      </c>
-      <c r="G342">
-        <v>161</v>
-      </c>
-      <c r="H342">
-        <v>-0.1</v>
-      </c>
-      <c r="I342">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2">
-        <v>45721</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D343">
-        <v>32.05555555555556</v>
-      </c>
-      <c r="E343">
-        <v>37.92</v>
-      </c>
-      <c r="F343">
-        <v>7.86</v>
-      </c>
-      <c r="G343">
-        <v>163.9</v>
-      </c>
-      <c r="H343">
-        <v>-0.08</v>
-      </c>
-      <c r="I343">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2">
-        <v>45722</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D344">
-        <v>24</v>
-      </c>
-      <c r="E344">
-        <v>36.41</v>
-      </c>
-      <c r="F344">
-        <v>7.84</v>
-      </c>
-      <c r="G344">
-        <v>200.2</v>
-      </c>
-      <c r="H344">
-        <v>-0.13</v>
-      </c>
-      <c r="I344">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2">
-        <v>45723</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D345">
-        <v>24.05555555555556</v>
-      </c>
-      <c r="E345">
-        <v>34.82</v>
-      </c>
-      <c r="F345">
-        <v>7.84</v>
-      </c>
-      <c r="G345">
-        <v>163.4</v>
-      </c>
-      <c r="H345">
-        <v>-0.12</v>
-      </c>
-      <c r="I345">
-        <v>-3.17</v>
-      </c>
-      <c r="K345">
-        <v>0</v>
-      </c>
-      <c r="L345">
-        <v>0</v>
-      </c>
-      <c r="M345">
-        <v>1.3</v>
-      </c>
-      <c r="N345">
-        <v>1.9</v>
-      </c>
-      <c r="O345">
-        <v>99</v>
-      </c>
-      <c r="P345">
-        <v>0.34</v>
-      </c>
-      <c r="Q345">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="2">
-        <v>45728</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D346">
-        <v>23.88888888888889</v>
-      </c>
-      <c r="E346">
-        <v>34.46</v>
-      </c>
-      <c r="F346">
-        <v>7.97</v>
-      </c>
-      <c r="G346">
-        <v>199.7</v>
-      </c>
-      <c r="H346">
-        <v>2.65</v>
-      </c>
-      <c r="I346">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="2">
-        <v>45729</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D347">
-        <v>24.05555555555556</v>
-      </c>
-      <c r="E347">
-        <v>34.2</v>
-      </c>
-      <c r="F347">
-        <v>8</v>
-      </c>
-      <c r="G347">
-        <v>177.5</v>
-      </c>
-      <c r="H347">
-        <v>0</v>
-      </c>
-      <c r="I347">
-        <v>-3.38</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2">
-        <v>45730</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D348">
-        <v>24.22222222222222</v>
-      </c>
-      <c r="E348">
-        <v>34.33</v>
-      </c>
-      <c r="F348">
-        <v>7.95</v>
-      </c>
-      <c r="G348">
-        <v>175.4</v>
-      </c>
-      <c r="H348">
-        <v>4.34</v>
-      </c>
-      <c r="I348">
-        <v>-3.31</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2">
-        <v>45733</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D349">
-        <v>23.94444444444444</v>
-      </c>
-      <c r="E349">
-        <v>34.43</v>
-      </c>
-      <c r="F349">
-        <v>7.92</v>
-      </c>
-      <c r="G349">
-        <v>155.3</v>
-      </c>
-      <c r="H349">
-        <v>1.93</v>
-      </c>
-      <c r="I349">
-        <v>-3.32</v>
-      </c>
-      <c r="J349">
-        <v>3.2832</v>
-      </c>
-      <c r="K349">
-        <v>0</v>
-      </c>
-      <c r="L349">
-        <v>0.03</v>
-      </c>
-      <c r="M349">
-        <v>1.5</v>
-      </c>
-      <c r="N349">
+      <c r="N307">
         <v>2.4</v>
       </c>
-      <c r="O349">
+      <c r="O307">
         <v>178</v>
       </c>
-      <c r="R349">
-        <v>0</v>
-      </c>
-      <c r="S349">
+      <c r="R307">
+        <v>0</v>
+      </c>
+      <c r="S307">
         <v>401</v>
       </c>
     </row>
